--- a/lista_precios_clientes.xlsx
+++ b/lista_precios_clientes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,9 +57,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -523,2121 +528,2132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina doctora</t>
+          <t>Caramelera Calabaza</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>24350</v>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Jardinera</t>
+          <t>Disfraz de Araña</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>24350</v>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Coqueta</t>
+          <t>Disfraz de Brujita Fuxia</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>24350</v>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>25500</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Deportiva</t>
+          <t>Disfraz de Brujita Naranja</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>24350</v>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>25500</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Romántica</t>
+          <t>Disfraz de Brujita Verde</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>24350</v>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>25500</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Folk</t>
+          <t>Disfraz de Brujita Violeta</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>24350</v>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>25500</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Bella</t>
+          <t>Disfraz de Calabaza</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>24350</v>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Cenicienta</t>
+          <t>Disfraz de Esqueleto</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>24350</v>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>25000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Blancanieves</t>
+          <t>Disfraz de Merlina</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>24350</v>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>32000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Aurora</t>
+          <t>Disfraz de Vampira</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>24350</v>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>25300</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Rapunsel</t>
+          <t>Disfraz de Zoey  K-Pop Demon Hunters</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>24350</v>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Sofía</t>
+          <t>Cesto para juguetes Cactus</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>24350</v>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>22900</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Traje de doctora para muñecas</t>
+          <t>Cesto para juguetes Cebra y Jirafa</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>8300</v>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>22900</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Traje de jardinera para muñecas</t>
+          <t>Cesto para juguetes Gatitos</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>8300</v>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>22900</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Vestido coqueta para muñecas</t>
+          <t>Cesto para juguetes Indi</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>8300</v>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>22900</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Traje deportivo para muñecas</t>
+          <t>Mini teatro Barco Pirata con Títeres de dedo de Piratas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>16300</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Vestido romántico para muñecas</t>
+          <t>Mini teatro Bosque con Títeres de dedo del Cuento Blancanieves y los Siete Enanitos</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>18800</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Vestido campesino para muñecas</t>
+          <t>Mini teatro Bosque con Títeres de dedo del Cuento de Caperucita Roja</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>16300</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Vestido de Bella para muñecas</t>
+          <t>Mini teatro Bosque con Títeres de dedo del cuento Los Tres Chanchitos y el Lobo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>16300</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Vestido de Cenicienta para muñecas</t>
+          <t>Mini teatro Castillo con Títeres de dedo de Cuento Príncipe Encantado</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Vestido de Blancanieves para muñecas</t>
+          <t>Mini teatro Castillo con Títeres de dedo de Cuento de Hadas</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>18800</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Vestido de Aurora para muñecas</t>
+          <t>Mini teatro Castillo con Títeres de dedo de Heroínas de Cuento</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>18800</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>21250</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>23670</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>26100</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Vestido de Rapunzel para muñecas</t>
+          <t>Mini teatro Circo con  Títeres de dedo de Artistas</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>18800</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Vestido de Princesa Sofía para muñecas</t>
+          <t>Mini teatro Ciudad con Títeres de dedo de  Animalitos Domésticos</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>18150</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>19920</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>21800</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>23550</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Ponis</t>
+          <t>Mini teatro Ciudad con Títeres de dedo de La Familia</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>19500</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>16300</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>18150</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>19920</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>21800</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Sirenitas</t>
+          <t>Mini teatro Ciudad con Títeres de dedo de Superhéroes</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>19500</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>18800</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Dinosaurios</t>
+          <t>Mini teatro Fondo del Mar con Títeres de dedo de La Sirenita</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>19500</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>19980</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Piratas</t>
+          <t>Mini teatro Prehistoria con Títeres de dedo de Dinosaurios y Cavernícolas</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>19500</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>14500</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>16200</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>19360</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Superhéroes</t>
+          <t>Mini teatro Selva con Títeres de dedo de la Selva Africana</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>19500</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>16300</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>18150</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>19920</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>21800</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>23550</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Haditas</t>
+          <t>Mini teatro de los Esteros del iberá con Títeres de dedo de animalitos de Los Esteros del Iberá</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>19500</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>19950</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Valija de Mini Maestra</t>
+          <t>Mini teatro granja con títeres de dedo de La Granja Arcoiris</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>28600</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>16300</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>18150</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>19920</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>21800</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>23550</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>25350</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>27200</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Valija de Mini Maestro</t>
+          <t>Miniteatro de Selva Misionera Argentina con Títeres de dedo de la Selva Misionera Argentina</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>28600</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>18200</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Valija de Mini Chef nena</t>
+          <t>Títeres de dedo Pack x 10 unidades de animalitos</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>21000</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Valija de Mini Chef varón</t>
+          <t>Títeres de dedo de Animalitos domésticos</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>21000</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>7800</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>9600</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>11400</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>13200</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Valija de Mini Jardineros</t>
+          <t>Títeres de dedo de Caperucita roja</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>23500</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>7800</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Valija de Mini Veterinarios</t>
+          <t>Títeres de dedo de Cuento Príncipe Encantado</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>26400</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>10300</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Valija de Mini Spa</t>
+          <t>Títeres de dedo de Cuento de Hadas</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>29800</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>10300</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Valija de Tarde de Mate</t>
+          <t>Títeres de dedo de El Circo Mágico</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>19500</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>10300</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Valija de Tardes de Té</t>
+          <t>Títeres de dedo de Heroínas de cuento</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>25000</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>10300</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>12700</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>17600</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Valija de Mini Exploradores</t>
+          <t>Títeres de dedo de La Familia Monte Espino</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>24800</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>7800</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>9600</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>11400</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>13200</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Valija de Mini Doctor</t>
+          <t>Títeres de dedo de La Prehistoria</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>37500</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>10825</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bolsito Explorador Jirafas</t>
+          <t>Títeres de dedo de La Sirenita</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>11500</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>11450</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Bolsito Explorador África</t>
+          <t>Títeres de dedo de Los Esteros del Iberá</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>11500</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>7800</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>9600</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>11400</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>13200</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bolsito Chef varón</t>
+          <t>Títeres de dedo de Los Piratas Siete Mares</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>11500</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>7800</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bolsito Chef nena</t>
+          <t>Títeres de dedo de Los Tres Chanchitos y el lobo</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>11500</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>7800</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Bolsito Mini Peluquería</t>
+          <t>Títeres de dedo de Selva Africana</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>11500</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>7800</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>9600</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>11400</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>13200</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>15100</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Set de esqueleto y órganos del cuerpo humano para Docentes y Educadores</t>
+          <t>Títeres de dedo de Selva Misionera</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>16500</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>7800</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>9600</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Rayuela de tela para aprender los números jugando</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>24500</v>
+          <t>Títeres de dedo de Superhéroes</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>10300</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Libro para bebé "Cosquillitas"</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>8400</v>
+          <t>Títeres de dedo de granja</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>7800</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>9600</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>11400</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>13200</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>15100</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Libro para bebé "Mariposas"</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>8400</v>
+          <t>Títeres de dedo del Cuento Blancanieves y los siete enanitos</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>10300</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Libro para bebé "Coral"</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>8400</v>
+          <t>Muñeca Piccolina Aurora</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Manta para bebé "La Ciudad"</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>15600</v>
+          <t>Muñeca Piccolina Bella</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Manta para bebé "Animalitos de la Selva"</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>15600</v>
+          <t>Muñeca Piccolina Blancanieves</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Manta para bebé "Mininos"</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>15600</v>
+          <t>Muñeca Piccolina Cenicienta</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Globo Pelota Monstruos</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>6800</v>
+          <t>Muñeca Piccolina Coqueta</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Globo Pelota Dinosaurios</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>6800</v>
+          <t>Muñeca Piccolina Deportiva</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Globo Pelota Haditas</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>6800</v>
+          <t>Muñeca Piccolina Folk</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Globo Pelota Animalitos</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>6800</v>
+          <t>Muñeca Piccolina Jardinera</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Globo Pelota Selva</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>6800</v>
+          <t>Muñeca Piccolina Rapunsel</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Globo Pelota Gatitos</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>6800</v>
+          <t>Muñeca Piccolina Romántica</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Pelota de Trapo  Dinosaurios</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>15950</v>
+          <t>Muñeca Piccolina Sofía</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Pelota de Trapo  Animalitos</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>15950</v>
+          <t>Muñeca Piccolina doctora</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Pelota de Trapo Selva</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>15950</v>
+          <t>Traje de doctora para muñecas</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>8300</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Pelota de Trapo Gatitos</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>15950</v>
+          <t>Traje de jardinera para muñecas</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>8300</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Pulpitos Reversibles con dos emociones (alegre/ enojado)</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>7500</v>
+          <t>Traje deportivo para muñecas</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>8300</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cesto para juguetes Cactus</t>
+          <t>Vestido campesino para muñecas</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>22900</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>8300</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cesto para juguetes Indi</t>
+          <t>Vestido coqueta para muñecas</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>22900</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>8300</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cesto para juguetes Cebra y Jirafa</t>
+          <t>Vestido de Aurora para muñecas</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>22900</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>8300</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cesto para juguetes Gatitos</t>
+          <t>Vestido de Bella para muñecas</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>22900</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>8300</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mini teatro granja con títeres de dedo de La Granja Arcoiris</t>
+          <t>Vestido de Blancanieves para muñecas</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G71" t="n">
-        <v>16300</v>
-      </c>
-      <c r="H71" t="n">
-        <v>18150</v>
-      </c>
-      <c r="I71" t="n">
-        <v>19920</v>
-      </c>
-      <c r="J71" t="n">
-        <v>21800</v>
-      </c>
-      <c r="K71" t="n">
-        <v>23550</v>
-      </c>
-      <c r="L71" t="n">
-        <v>25350</v>
-      </c>
-      <c r="M71" t="n">
-        <v>27200</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>8300</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Mini teatro Selva con Títeres de dedo de la Selva Africana</t>
+          <t>Vestido de Cenicienta para muñecas</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G72" t="n">
-        <v>16300</v>
-      </c>
-      <c r="H72" t="n">
-        <v>18150</v>
-      </c>
-      <c r="I72" t="n">
-        <v>19920</v>
-      </c>
-      <c r="J72" t="n">
-        <v>21800</v>
-      </c>
-      <c r="K72" t="n">
-        <v>23550</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>8300</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Miniteatro de Selva Misionera Argentina con Títeres de dedo de la Selva Misionera Argentina</t>
+          <t>Vestido de Princesa Sofía para muñecas</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>18200</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>8300</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Mini teatro de los Esteros del iberá con Títeres de dedo de animalitos de Los Esteros del Iberá</t>
+          <t>Vestido de Rapunzel para muñecas</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>19950</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>8300</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Mini teatro Castillo con Títeres de dedo de Cuento de Hadas</t>
+          <t>Vestido romántico para muñecas</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>18800</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>8300</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Mini teatro Castillo con Títeres de dedo de Cuento Príncipe Encantado</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>18000</v>
+          <t>Blancanieves y los Siete Enanitos. Títeres de Mano y de Dedo.</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>29450</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Mini teatro Castillo con Títeres de dedo de Heroínas de Cuento</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G77" t="n">
-        <v>18800</v>
-      </c>
-      <c r="H77" t="n">
-        <v>21250</v>
-      </c>
-      <c r="I77" t="n">
-        <v>23670</v>
-      </c>
-      <c r="J77" t="n">
-        <v>26100</v>
+          <t>Bolsito Amasando ideas Elefante</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Mini teatro Fondo del Mar con Títeres de dedo de La Sirenita</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>19980</v>
+          <t>Bolsito Amasando ideas Espacio</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Mini teatro Circo con  Títeres de dedo de Artistas</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>18800</v>
+          <t>Bolsito Amasando ideas Gato automovilista</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Mini teatro Barco Pirata con Títeres de dedo de Piratas</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>16300</v>
+          <t>Bolsito Amasando ideas Pajaritos</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Mini teatro Bosque con Títeres de dedo del cuento Los Tres Chanchitos y el Lobo</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>16300</v>
+          <t>Caperucita Roja. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>20300</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Mini teatro Bosque con Títeres de dedo del Cuento de Caperucita Roja</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>16300</v>
+          <t>Cuento de Hadas. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>20300</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Mini teatro Bosque con Títeres de dedo del Cuento Blancanieves y los Siete Enanitos</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>18800</v>
+          <t>Cuento de Príncipe Sapo y su Princesa. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>20300</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Mini teatro Ciudad con Títeres de dedo de Superhéroes</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>18800</v>
+          <t>Disfraz de Anna (Frozen)</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>24850</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Mini teatro Ciudad con Títeres de dedo de La Familia</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G85" t="n">
-        <v>16300</v>
-      </c>
-      <c r="H85" t="n">
-        <v>18150</v>
-      </c>
-      <c r="I85" t="n">
-        <v>19920</v>
-      </c>
-      <c r="J85" t="n">
-        <v>21800</v>
+          <t>Disfraz de Araña</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Mini teatro Ciudad con Títeres de dedo de  Animalitos Domésticos</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="H86" t="n">
-        <v>18150</v>
-      </c>
-      <c r="I86" t="n">
-        <v>19920</v>
-      </c>
-      <c r="J86" t="n">
-        <v>21800</v>
-      </c>
-      <c r="K86" t="n">
-        <v>23550</v>
+          <t>Disfraz de Batman</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Mini teatro Prehistoria con Títeres de dedo de Dinosaurios y Cavernícolas</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>14500</v>
-      </c>
-      <c r="G87" t="n">
-        <v>16200</v>
-      </c>
-      <c r="H87" t="n">
-        <v>19360</v>
+          <t>Disfraz de Bella</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>23970</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Tutú de bailarina</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>19500</v>
+          <t>Disfraz de Blancanieves</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>24850</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Tutú de Bailarina Unicornio</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>23200</v>
+          <t>Disfraz de Bombero</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Disfraz de Mujer Maravilla</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>19850</v>
+          <t>Disfraz de Capitán América</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Disfraz de Rapunzel Encantada</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>33300</v>
+          <t>Disfraz de Cebra</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Disfraz de Princesa Aurora,  La Bella Durmiente</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
+          <t>Disfraz de Cenicienta</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
         <v>23970</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Disfraz de Cenicienta</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>23970</v>
+          <t>Disfraz de Dinosaurio</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>25200</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Disfraz de Bella</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>23970</v>
+          <t>Disfraz de Elsa (Frozen)</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>24850</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Disfraz de Blancanieves</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>24850</v>
+          <t>Disfraz de Hombre Araña</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Disfraz de Elsa (Frozen)</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>24850</v>
+          <t>Disfraz de Mira K-Pop Demon Hunters</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>38500</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Disfraz de Anna (Frozen)</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>24850</v>
+          <t>Disfraz de Moana</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>24500</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Disfraz de Unicornio Mágico</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>27400</v>
+          <t>Disfraz de Mujer Maravilla</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>19850</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Disfraz de Sirenita</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>22500</v>
+          <t>Disfraz de Pirata</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Disfraz de Moana</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>24500</v>
+          <t>Disfraz de Policía</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Disfraz de Mira K-Pop Demon Hunters</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>38500</v>
+          <t>Disfraz de Princesa Aurora,  La Bella Durmiente</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>23970</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Disfraz de Rumi K-Pop Demon Hunters</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>28500</v>
+          <t>Disfraz de Rapunzel Encantada</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>33300</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Disfraz de Zoey  K-Pop Demon Hunters</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>45000</v>
+          <t>Disfraz de Rumi K-Pop Demon Hunters</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>28500</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Disfraz de Rumi K-Pop Demon Hunters, con Chaqueta y encanto dorado</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>53200</v>
+          <t>Disfraz de Rumi K-Pop Demon Hunters (Traje de colores con Chaqueta amarilla)</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>51800</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Disfraz de Rumi K-Pop Demon Hunters (Traje de colores con Chaqueta amarilla)</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>51800</v>
+          <t>Disfraz de Rumi K-Pop Demon Hunters, con Chaqueta y encanto dorado</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>53200</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Disfraz de Vampira</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>25300</v>
+          <t>Disfraz de Sirenita</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>22500</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Disfraz de Merlina</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>32000</v>
+          <t>Disfraz de Superman</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>22000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Violeta</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>25500</v>
+          <t>Disfraz de Tigre</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Naranja</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>25500</v>
+          <t>Disfraz de Unicornio Mágico</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>27400</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Verde</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>25500</v>
+          <t>El Circo Mágico. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>20300</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Fuxia</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>25500</v>
+          <t>El Pesebre de Navideño. Títeres de Mano.</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>41200</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Disfraz de Esqueleto</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>25000</v>
+          <t>Globo Pelota Animalitos</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>6800</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Disfraz de Calabaza</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>23500</v>
+          <t>Globo Pelota Dinosaurios</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>6800</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Disfraz de Araña</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>23500</v>
+          <t>Globo Pelota Gatitos</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>6800</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Caramelera Calabaza</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>9000</v>
+          <t>Globo Pelota Haditas</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>6800</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Disfraz de Pirata</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>18000</v>
+          <t>Globo Pelota Monstruos</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>6800</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Disfraz de Hombre Araña</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>18000</v>
+          <t>Globo Pelota Selva</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>6800</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Disfraz de Superman</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>22000</v>
+          <t>Heroínas de Cuentos Clásicos. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>15400</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>20300</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>25200</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>30200</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>35100</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Disfraz de Capitán América</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>23500</v>
+          <t>La Familia Monte Espino. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>20300</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>25200</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>30200</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>35100</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>39960</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>44900</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>54750</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Disfraz de Batman</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>23500</v>
+          <t>La Granja Arcoíris. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>11850</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>16500</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>19700</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>22860</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>26100</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>29300</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>33200</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>35700</v>
+      </c>
+      <c r="O120" s="2" t="n">
+        <v>38800</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Disfraz de Dinosaurio</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>25200</v>
+          <t>La Prehistoria: Dinosaurios y Cavernícolas. Títeres de mano.</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>11200</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>19960</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Disfraz de Cebra</t>
-        </is>
-      </c>
-      <c r="C122" t="n">
-        <v>23500</v>
+          <t>La Selva Africana. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>11850</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>16500</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>19700</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>22860</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>26100</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Disfraz de Tigre</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>23500</v>
+          <t>La Selva Misionera Argentina. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>19000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Disfraz de Araña</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>23500</v>
+          <t>La Sirenita. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>25200</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Disfraz de Bombero</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>15000</v>
+          <t>Las Emociones. Títeres de Mano de Nena</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v>30200</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Disfraz de Policía</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>15000</v>
+          <t>Las Emociones. Títeres de Mano de Nene</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v>30200</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Los Esteros del Iberá. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>23200</v>
+          <t>Libro para bebé "Coral"</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v>8400</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>La Granja Arcoíris. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="G128" t="n">
-        <v>11850</v>
-      </c>
-      <c r="H128" t="n">
-        <v>16500</v>
-      </c>
-      <c r="I128" t="n">
-        <v>19700</v>
-      </c>
-      <c r="J128" t="n">
-        <v>22860</v>
-      </c>
-      <c r="K128" t="n">
-        <v>26100</v>
-      </c>
-      <c r="L128" t="n">
-        <v>29300</v>
-      </c>
-      <c r="M128" t="n">
-        <v>33200</v>
-      </c>
-      <c r="N128" t="n">
-        <v>35700</v>
-      </c>
-      <c r="O128" t="n">
-        <v>38800</v>
+          <t>Libro para bebé "Cosquillitas"</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="n">
+        <v>8400</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Mis amigos los animalitos domésticos . Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="H129" t="n">
-        <v>16500</v>
-      </c>
-      <c r="J129" t="n">
-        <v>26350</v>
+          <t>Libro para bebé "Mariposas"</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v>8400</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>La Selva Africana. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="G130" t="n">
+          <t>Los 3 Chanchitos y el Lobo Feroz . Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n">
         <v>11850</v>
-      </c>
-      <c r="H130" t="n">
-        <v>16500</v>
-      </c>
-      <c r="I130" t="n">
-        <v>19700</v>
-      </c>
-      <c r="J130" t="n">
-        <v>22860</v>
-      </c>
-      <c r="K130" t="n">
-        <v>26100</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>La Selva Misionera Argentina. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>19000</v>
+          <t>Los Esteros del Iberá. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v>23200</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Cuento de Hadas. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
+          <t>Los Piratas Siete Mares. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
         <v>20300</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Cuento de Príncipe Sapo y su Princesa. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>20300</v>
+          <t>Manta para bebé "Animalitos de la Selva"</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="n">
+        <v>15600</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>La Sirenita. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>25200</v>
+          <t>Manta para bebé "La Ciudad"</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="n">
+        <v>15600</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>El Circo Mágico. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>20300</v>
+          <t>Manta para bebé "Mininos"</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="n">
+        <v>15600</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Los Piratas Siete Mares. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>20300</v>
+          <t>Mis amigos los animalitos domésticos . Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>16500</v>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v>26350</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Los 3 Chanchitos y el Lobo Feroz . Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>11850</v>
+          <t>Navidad. Títeres de Mano.</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>11200</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Caperucita Roja. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>20300</v>
+          <t>Pelota de Trapo  Animalitos</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>15950</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Heroínas de Cuentos Clásicos. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="F139" t="n">
-        <v>15400</v>
-      </c>
-      <c r="G139" t="n">
-        <v>20300</v>
-      </c>
-      <c r="H139" t="n">
-        <v>25200</v>
-      </c>
-      <c r="I139" t="n">
-        <v>30200</v>
-      </c>
-      <c r="J139" t="n">
-        <v>35100</v>
+          <t>Pelota de Trapo  Dinosaurios</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>15950</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Blancanieves y los Siete Enanitos. Títeres de Mano y de Dedo.</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>29450</v>
+          <t>Pelota de Trapo Gatitos</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v>15950</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>La Familia Monte Espino. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="G141" t="n">
-        <v>20300</v>
-      </c>
-      <c r="H141" t="n">
-        <v>25200</v>
-      </c>
-      <c r="I141" t="n">
-        <v>30200</v>
-      </c>
-      <c r="J141" t="n">
-        <v>35100</v>
-      </c>
-      <c r="K141" t="n">
-        <v>39960</v>
-      </c>
-      <c r="L141" t="n">
-        <v>44900</v>
-      </c>
-      <c r="M141" t="n">
-        <v>54750</v>
+          <t>Pelota de Trapo Selva</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>15950</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Superhéroes. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>20300</v>
+          <t>Pulpitos Reversibles con dos emociones (alegre/ enojado)</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>7500</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Títeres Patrios. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="G143" t="n">
-        <v>11850</v>
-      </c>
-      <c r="H143" t="n">
-        <v>16500</v>
-      </c>
-      <c r="I143" t="n">
-        <v>19700</v>
-      </c>
-      <c r="J143" t="n">
-        <v>22860</v>
-      </c>
-      <c r="K143" t="n">
-        <v>26100</v>
-      </c>
-      <c r="L143" t="n">
-        <v>29300</v>
-      </c>
-      <c r="M143" t="n">
-        <v>33200</v>
-      </c>
-      <c r="N143" t="n">
-        <v>35700</v>
-      </c>
-      <c r="O143" t="n">
-        <v>38800</v>
+          <t>Rayuela de tela para aprender los números jugando</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>24500</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Navidad. Títeres de Mano.</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
-        <v>11200</v>
+          <t>Superhéroes. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n">
+        <v>20300</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>El Pesebre de Navideño. Títeres de Mano.</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>41200</v>
+          <t>Teatro "El Circo Mágico" con Títeres de Artistas</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n">
+        <v>36800</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>La Prehistoria: Dinosaurios y Cavernícolas. Títeres de mano.</t>
-        </is>
-      </c>
-      <c r="F146" t="n">
-        <v>11200</v>
-      </c>
-      <c r="H146" t="n">
-        <v>19960</v>
+          <t>Teatro Barco con Títeres de Los Piratas de los Siete Mares.</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>36800</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Las Emociones. Títeres de Mano de Nene</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>30200</v>
+          <t>Teatro Bosque con Títeres del cuento "Los tres Chanchitos y el Lobo Feroz"</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v>29800</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Las Emociones. Títeres de Mano de Nena</t>
-        </is>
-      </c>
-      <c r="C148" t="n">
-        <v>30200</v>
+          <t>Teatro Castillo con Títeres de Cuento de Hadas</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n">
+        <v>36800</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Teatro Granja con Títeres de La Granja</t>
-        </is>
-      </c>
-      <c r="G149" t="n">
-        <v>29800</v>
-      </c>
-      <c r="H149" t="n">
-        <v>32980</v>
-      </c>
-      <c r="I149" t="n">
-        <v>36200</v>
-      </c>
-      <c r="J149" t="n">
-        <v>39400</v>
-      </c>
-      <c r="K149" t="n">
+          <t>Teatro Castillo con Títeres de Heroínas de Cuentos Clásicos.</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>36800</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>41700</v>
+      </c>
+      <c r="I149" s="2" t="n">
         <v>46600</v>
       </c>
-      <c r="L149" t="n">
-        <v>45800</v>
-      </c>
-      <c r="M149" t="n">
-        <v>48950</v>
-      </c>
-      <c r="N149" t="n">
-        <v>52100</v>
-      </c>
-      <c r="O149" t="n">
-        <v>55300</v>
+      <c r="J149" s="2" t="n">
+        <v>48100</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Teatro Selva con Títeres de la Selva Africana</t>
-        </is>
-      </c>
-      <c r="G150" t="n">
-        <v>29800</v>
-      </c>
-      <c r="H150" t="n">
-        <v>32980</v>
-      </c>
-      <c r="I150" t="n">
-        <v>36200</v>
-      </c>
-      <c r="J150" t="n">
-        <v>39400</v>
-      </c>
-      <c r="K150" t="n">
-        <v>46600</v>
+          <t>Teatro Castillo con Títeres del Cuento "Príncipe Sapo y su Princesa"</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v>36800</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Teatro Selva Misionera Argentina con Títeres de la Selva Misionera</t>
-        </is>
-      </c>
-      <c r="C151" t="n">
-        <v>32980</v>
+          <t>Teatro Ciudad con Títeres de La Familia Monte Espino</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="n">
+        <v>36800</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>41700</v>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>46600</v>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>48100</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Teatro de los Esteros del Iberá Títeres de animales de los Esteros del Iberá</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
-        <v>36200</v>
+          <t>Teatro Ciudad con Títeres de Nene y sus Emociones</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>36800</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>41700</v>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>46600</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Teatro Castillo con Títeres de Cuento de Hadas</t>
-        </is>
-      </c>
-      <c r="C153" t="n">
+          <t>Teatro Ciudad con Títeres de nena y sus Emociones</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="n">
         <v>36800</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>41700</v>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>46600</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Teatro bosque con Títeres de Caperucita Roja</t>
-        </is>
-      </c>
-      <c r="C154" t="n">
+          <t>Teatro Ciudad con títeres de niños animalitos domésticos</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="n">
         <v>36800</v>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>41700</v>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>46600</v>
       </c>
     </row>
     <row r="155">
@@ -2646,270 +2662,294 @@
           <t>Teatro Fondo del mar con Títeres de "La Sirenita"</t>
         </is>
       </c>
-      <c r="C155" t="n">
+      <c r="C155" s="2" t="n">
         <v>38200</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Teatro Barco con Títeres de Los Piratas de los Siete Mares.</t>
-        </is>
-      </c>
-      <c r="C156" t="n">
-        <v>36800</v>
+          <t>Teatro Granja con Títeres de La Granja</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="n">
+        <v>29800</v>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>32980</v>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>36200</v>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>39400</v>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>46600</v>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>45800</v>
+      </c>
+      <c r="M156" s="2" t="n">
+        <v>48950</v>
+      </c>
+      <c r="N156" s="2" t="n">
+        <v>52100</v>
+      </c>
+      <c r="O156" s="2" t="n">
+        <v>55300</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Teatro Bosque con Títeres del cuento "Los tres Chanchitos y el Lobo Feroz"</t>
-        </is>
-      </c>
-      <c r="C157" t="n">
-        <v>29800</v>
+          <t>Teatro Prehistoria con Títeres de Dinosaurios y Cavernícolas</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>28900</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>36500</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con Títeres de La Familia Monte Espino</t>
-        </is>
-      </c>
-      <c r="G158" t="n">
-        <v>36800</v>
-      </c>
-      <c r="H158" t="n">
-        <v>41700</v>
-      </c>
-      <c r="I158" t="n">
-        <v>46600</v>
-      </c>
-      <c r="J158" t="n">
-        <v>48100</v>
+          <t>Teatro Selva Misionera Argentina con Títeres de la Selva Misionera</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="n">
+        <v>32980</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Teatro de la Época Colonial con Títeres Patrios</t>
-        </is>
-      </c>
-      <c r="G159" t="n">
+          <t>Teatro Selva con Títeres de la Selva Africana</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="n">
         <v>29800</v>
       </c>
-      <c r="H159" t="n">
+      <c r="H159" s="2" t="n">
         <v>32980</v>
       </c>
-      <c r="I159" t="n">
+      <c r="I159" s="2" t="n">
         <v>36200</v>
       </c>
-      <c r="J159" t="n">
+      <c r="J159" s="2" t="n">
         <v>39400</v>
       </c>
-      <c r="K159" t="n">
+      <c r="K159" s="2" t="n">
         <v>46600</v>
-      </c>
-      <c r="L159" t="n">
-        <v>45800</v>
-      </c>
-      <c r="M159" t="n">
-        <v>48950</v>
-      </c>
-      <c r="N159" t="n">
-        <v>52100</v>
-      </c>
-      <c r="O159" t="n">
-        <v>55300</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Teatro Castillo con Títeres del Cuento "Príncipe Sapo y su Princesa"</t>
-        </is>
-      </c>
-      <c r="C160" t="n">
+          <t>Teatro bosque con Títeres de Caperucita Roja</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n">
         <v>36800</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Teatro Castillo con Títeres de Heroínas de Cuentos Clásicos.</t>
-        </is>
-      </c>
-      <c r="G161" t="n">
-        <v>36800</v>
-      </c>
-      <c r="H161" t="n">
-        <v>41700</v>
-      </c>
-      <c r="I161" t="n">
-        <v>46600</v>
-      </c>
-      <c r="J161" t="n">
-        <v>48100</v>
+          <t>Teatro bosque con títeres de Blancanieves y los Siete Enanitos</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>34990</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Teatro "El Circo Mágico" con Títeres de Artistas</t>
-        </is>
-      </c>
-      <c r="C162" t="n">
+          <t>Teatro ciudad con títeres de Superhéroes.</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="n">
         <v>36800</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Teatro bosque con títeres de Blancanieves y los Siete Enanitos</t>
-        </is>
-      </c>
-      <c r="C163" t="n">
-        <v>34990</v>
+          <t>Teatro de Títeres Didáctico Clásico para Escuelas y Jardines de Infantes</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>57800</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Teatro ciudad con títeres de Superhéroes.</t>
-        </is>
-      </c>
-      <c r="C164" t="n">
-        <v>36800</v>
+          <t>Teatro de la Época Colonial con Títeres Patrios</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="n">
+        <v>29800</v>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>32980</v>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>36200</v>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>39400</v>
+      </c>
+      <c r="K164" s="2" t="n">
+        <v>46600</v>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>45800</v>
+      </c>
+      <c r="M164" s="2" t="n">
+        <v>48950</v>
+      </c>
+      <c r="N164" s="2" t="n">
+        <v>52100</v>
+      </c>
+      <c r="O164" s="2" t="n">
+        <v>55300</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Teatro Prehistoria con Títeres de Dinosaurios y Cavernícolas</t>
-        </is>
-      </c>
-      <c r="F165" t="n">
-        <v>28900</v>
-      </c>
-      <c r="H165" t="n">
-        <v>36500</v>
+          <t>Teatro de los Esteros del Iberá Títeres de animales de los Esteros del Iberá</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="n">
+        <v>36200</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con títeres de niños animalitos domésticos</t>
-        </is>
-      </c>
-      <c r="G166" t="n">
-        <v>36800</v>
-      </c>
-      <c r="H166" t="n">
-        <v>41700</v>
-      </c>
-      <c r="I166" t="n">
-        <v>46600</v>
+          <t>Tutú de Bailarina Unicornio</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="n">
+        <v>23200</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con Títeres de nena y sus Emociones</t>
-        </is>
-      </c>
-      <c r="G167" t="n">
-        <v>36800</v>
-      </c>
-      <c r="H167" t="n">
-        <v>41700</v>
-      </c>
-      <c r="I167" t="n">
-        <v>46600</v>
+          <t>Tutú de bailarina</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con Títeres de Nene y sus Emociones</t>
-        </is>
-      </c>
-      <c r="G168" t="n">
-        <v>36800</v>
-      </c>
-      <c r="H168" t="n">
-        <v>41700</v>
-      </c>
-      <c r="I168" t="n">
-        <v>46600</v>
+          <t>Títeres Patrios. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="n">
+        <v>11850</v>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>16500</v>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>19700</v>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>22860</v>
+      </c>
+      <c r="K168" s="2" t="n">
+        <v>26100</v>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>29300</v>
+      </c>
+      <c r="M168" s="2" t="n">
+        <v>33200</v>
+      </c>
+      <c r="N168" s="2" t="n">
+        <v>35700</v>
+      </c>
+      <c r="O168" s="2" t="n">
+        <v>38800</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Teatro de Títeres Didáctico Clásico para Escuelas y Jardines de Infantes</t>
-        </is>
-      </c>
-      <c r="C169" t="n">
-        <v>57800</v>
+          <t>Valija de Arte Mis Diseños. Astronautas</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="n">
+        <v>25850</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Nena en Hamaca</t>
-        </is>
-      </c>
-      <c r="C170" t="n">
+          <t>Valija de Arte Mis Diseños. Cocodrilo en Submarino</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="n">
         <v>25850</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Nena con Globos</t>
-        </is>
-      </c>
-      <c r="C171" t="n">
+          <t>Valija de Arte Mis Diseños. Gato Automovilista</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="n">
         <v>25850</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Unicornio</t>
-        </is>
-      </c>
-      <c r="C172" t="n">
+          <t>Valija de Arte Mis Diseños. Monstruos</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="n">
         <v>25850</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Princesa</t>
-        </is>
-      </c>
-      <c r="C173" t="n">
+          <t>Valija de Arte Mis Diseños. Nena con Globos</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="n">
         <v>25850</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Monstruos</t>
-        </is>
-      </c>
-      <c r="C174" t="n">
+          <t>Valija de Arte Mis Diseños. Nena en Hamaca</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="n">
         <v>25850</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Astronautas</t>
-        </is>
-      </c>
-      <c r="C175" t="n">
+          <t>Valija de Arte Mis Diseños. Princesa</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="n">
         <v>25850</v>
       </c>
     </row>
@@ -2919,398 +2959,363 @@
           <t>Valija de Arte Mis Diseños. Robots</t>
         </is>
       </c>
-      <c r="C176" t="n">
+      <c r="C176" s="2" t="n">
         <v>25850</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Gato Automovilista</t>
-        </is>
-      </c>
-      <c r="C177" t="n">
+          <t>Valija de Arte Mis Diseños. Unicornio</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="n">
         <v>25850</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Cocodrilo en Submarino</t>
-        </is>
-      </c>
-      <c r="C178" t="n">
-        <v>25850</v>
+          <t>Valija de Arte Mini Artista, Dinosaurios</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Bolsito Amasando ideas Elefante</t>
-        </is>
-      </c>
-      <c r="C179" t="n">
-        <v>12000</v>
+          <t>Valija de Arte Mini Artista, Haditas</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Bolsito Amasando ideas Pajaritos</t>
-        </is>
-      </c>
-      <c r="C180" t="n">
-        <v>12000</v>
+          <t>Valija de Arte Mini Artista, Piratas</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Bolsito Amasando ideas Espacio</t>
-        </is>
-      </c>
-      <c r="C181" t="n">
-        <v>12000</v>
+          <t>Valija de Arte Mini Artista, Ponis</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Bolsito Amasando ideas Gato automovilista</t>
-        </is>
-      </c>
-      <c r="C182" t="n">
-        <v>12000</v>
+          <t>Valija de Arte Mini Artista, Sirenitas</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Títeres de dedo de granja</t>
+          <t>Valija de Arte Mini Artista, Superhéroes</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G183" t="n">
-        <v>7800</v>
-      </c>
-      <c r="H183" t="n">
-        <v>9600</v>
-      </c>
-      <c r="I183" t="n">
-        <v>11400</v>
-      </c>
-      <c r="J183" t="n">
-        <v>13200</v>
-      </c>
-      <c r="K183" t="n">
-        <v>15100</v>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Selva Africana</t>
+          <t>Bolsito Chef nena</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G184" t="n">
-        <v>7800</v>
-      </c>
-      <c r="H184" t="n">
-        <v>9600</v>
-      </c>
-      <c r="I184" t="n">
-        <v>11400</v>
-      </c>
-      <c r="J184" t="n">
-        <v>13200</v>
-      </c>
-      <c r="K184" t="n">
-        <v>15100</v>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="n">
+        <v>11500</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Selva Misionera</t>
+          <t>Bolsito Chef varón</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G185" t="n">
-        <v>7800</v>
-      </c>
-      <c r="H185" t="n">
-        <v>9600</v>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="n">
+        <v>11500</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Los Esteros del Iberá</t>
+          <t>Bolsito Explorador Jirafas</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G186" t="n">
-        <v>7800</v>
-      </c>
-      <c r="H186" t="n">
-        <v>9600</v>
-      </c>
-      <c r="I186" t="n">
-        <v>11400</v>
-      </c>
-      <c r="J186" t="n">
-        <v>13200</v>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="n">
+        <v>11500</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Animalitos domésticos</t>
+          <t>Bolsito Explorador África</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G187" t="n">
-        <v>7800</v>
-      </c>
-      <c r="H187" t="n">
-        <v>9600</v>
-      </c>
-      <c r="I187" t="n">
-        <v>11400</v>
-      </c>
-      <c r="J187" t="n">
-        <v>13200</v>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="n">
+        <v>11500</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Cuento de Hadas</t>
+          <t>Bolsito Mini Peluquería</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C188" t="n">
-        <v>10300</v>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="n">
+        <v>11500</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Cuento Príncipe Encantado</t>
+          <t>Set de esqueleto y órganos del cuerpo humano para Docentes y Educadores</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C189" t="n">
-        <v>10300</v>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="n">
+        <v>16500</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Títeres de dedo de La Sirenita</t>
+          <t>Valija de Mini Chef nena</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C190" t="n">
-        <v>11450</v>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="n">
+        <v>21000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Heroínas de cuento</t>
+          <t>Valija de Mini Chef varón</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G191" t="n">
-        <v>10300</v>
-      </c>
-      <c r="H191" t="n">
-        <v>12700</v>
-      </c>
-      <c r="J191" t="n">
-        <v>17600</v>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="n">
+        <v>21000</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Títeres de dedo de El Circo Mágico</t>
+          <t>Valija de Mini Doctor</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C192" t="n">
-        <v>10300</v>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="n">
+        <v>37500</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Los Piratas Siete Mares</t>
+          <t>Valija de Mini Exploradores</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C193" t="n">
-        <v>7800</v>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="n">
+        <v>24800</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Los Tres Chanchitos y el lobo</t>
+          <t>Valija de Mini Jardineros</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C194" t="n">
-        <v>7800</v>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Caperucita roja</t>
+          <t>Valija de Mini Maestra</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C195" t="n">
-        <v>7800</v>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="n">
+        <v>28600</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Superhéroes</t>
+          <t>Valija de Mini Maestro</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C196" t="n">
-        <v>10300</v>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="n">
+        <v>28600</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Títeres de dedo de La Familia Monte Espino</t>
+          <t>Valija de Mini Spa</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G197" t="n">
-        <v>7800</v>
-      </c>
-      <c r="H197" t="n">
-        <v>9600</v>
-      </c>
-      <c r="I197" t="n">
-        <v>11400</v>
-      </c>
-      <c r="J197" t="n">
-        <v>13200</v>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="n">
+        <v>29800</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Títeres de dedo de La Prehistoria</t>
+          <t>Valija de Mini Veterinarios</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C198" t="n">
-        <v>10825</v>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="n">
+        <v>26400</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Títeres de dedo Pack x 10 unidades de animalitos</t>
+          <t>Valija de Tarde de Mate</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C199" t="n">
-        <v>18000</v>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Títeres de dedo del Cuento Blancanieves y los siete enanitos</t>
+          <t>Valija de Tardes de Té</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C200" t="n">
-        <v>10300</v>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="n">
+        <v>25000</v>
       </c>
     </row>
   </sheetData>

--- a/lista_precios_clientes.xlsx
+++ b/lista_precios_clientes.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,8 +30,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +46,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E8D8C0"/>
         <bgColor rgb="00E8D8C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4A62A"/>
+        <bgColor rgb="00F4A62A"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +67,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -428,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O200"/>
+  <dimension ref="A1:O211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -526,807 +539,870 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Caramelera Calabaza</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>9000</v>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TÍTERES DE MANO</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Disfraz de Araña</t>
+          <t>Blancanieves y los Siete Enanitos. Títeres de Mano y de Dedo.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>23500</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>29450</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Fuxia</t>
+          <t>Caperucita Roja. Títeres de Mano</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>25500</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>20300</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Naranja</t>
+          <t>Cuento de Hadas. Títeres de Mano</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>25500</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>20300</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Verde</t>
+          <t>Cuento de Príncipe Sapo y su Princesa. Títeres de Mano</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>25500</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>20300</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Violeta</t>
+          <t>El Circo Mágico. Títeres de Mano</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>25500</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>20300</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Disfraz de Calabaza</t>
+          <t>El Pesebre de Navideño. Títeres de Mano.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>23500</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>41200</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Disfraz de Esqueleto</t>
+          <t>Heroínas de Cuentos Clásicos. Títeres de Mano</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>25000</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>15400</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>20300</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>25200</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>30200</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>35100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Disfraz de Merlina</t>
+          <t>La Familia Monte Espino. Títeres de Mano</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>32000</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>20300</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>25200</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>30200</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>35100</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>39960</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>44900</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>54750</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Disfraz de Vampira</t>
+          <t>La Granja Arcoíris. Títeres de Mano</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>25300</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>11850</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>16500</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>19700</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>22860</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>26100</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>29300</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>33200</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>35700</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>38800</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Disfraz de Zoey  K-Pop Demon Hunters</t>
+          <t>La Prehistoria: Dinosaurios y Cavernícolas. Títeres de mano.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>45000</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>11200</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>19960</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cesto para juguetes Cactus</t>
+          <t>La Selva Africana. Títeres de Mano</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>22900</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>11850</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>16500</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>19700</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>22860</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>26100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cesto para juguetes Cebra y Jirafa</t>
+          <t>La Selva Misionera Argentina. Títeres de Mano</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>22900</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>19000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cesto para juguetes Gatitos</t>
+          <t>La Sirenita. Títeres de Mano</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>22900</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>25200</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cesto para juguetes Indi</t>
+          <t>Las Emociones. Títeres de Mano de Nena</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>22900</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>30200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mini teatro Barco Pirata con Títeres de dedo de Piratas</t>
+          <t>Las Emociones. Títeres de Mano de Nene</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>16300</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>30200</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mini teatro Bosque con Títeres de dedo del Cuento Blancanieves y los Siete Enanitos</t>
+          <t>Los 3 Chanchitos y el Lobo Feroz . Títeres de Mano</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>18800</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>11850</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mini teatro Bosque con Títeres de dedo del Cuento de Caperucita Roja</t>
+          <t>Los Esteros del Iberá. Títeres de Mano</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>16300</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>23200</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mini teatro Bosque con Títeres de dedo del cuento Los Tres Chanchitos y el Lobo</t>
+          <t>Los Piratas Siete Mares. Títeres de Mano</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>16300</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>20300</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mini teatro Castillo con Títeres de dedo de Cuento Príncipe Encantado</t>
+          <t>Mis amigos los animalitos domésticos . Títeres de Mano</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>18000</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>16500</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>26350</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mini teatro Castillo con Títeres de dedo de Cuento de Hadas</t>
+          <t>Navidad. Títeres de Mano.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>18800</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>11200</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mini teatro Castillo con Títeres de dedo de Heroínas de Cuento</t>
+          <t>Superhéroes. Títeres de Mano</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>18800</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>21250</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>23670</v>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>26100</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>20300</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mini teatro Circo con  Títeres de dedo de Artistas</t>
+          <t>Títeres Patrios. Títeres de Mano</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>18800</v>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>11850</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>16500</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>19700</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>22860</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>26100</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>29300</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>33200</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>35700</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>38800</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Mini teatro Ciudad con Títeres de dedo de  Animalitos Domésticos</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>18150</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>19920</v>
-      </c>
-      <c r="J25" s="2" t="n">
-        <v>21800</v>
-      </c>
-      <c r="K25" s="2" t="n">
-        <v>23550</v>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mini teatro Ciudad con Títeres de dedo de La Familia</t>
+          <t>Teatro "El Circo Mágico" con Títeres de Artistas</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>16300</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>18150</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>19920</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>21800</v>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>36800</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mini teatro Ciudad con Títeres de dedo de Superhéroes</t>
+          <t>Teatro Barco con Títeres de Los Piratas de los Siete Mares.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>18800</v>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>36800</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mini teatro Fondo del Mar con Títeres de dedo de La Sirenita</t>
+          <t>Teatro Bosque con Títeres del cuento "Los tres Chanchitos y el Lobo Feroz"</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>19980</v>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>29800</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mini teatro Prehistoria con Títeres de dedo de Dinosaurios y Cavernícolas</t>
+          <t>Teatro Castillo con Títeres de Cuento de Hadas</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>14500</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>16200</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>19360</v>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>36800</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mini teatro Selva con Títeres de dedo de la Selva Africana</t>
+          <t>Teatro Castillo con Títeres de Heroínas de Cuentos Clásicos.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>16300</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>18150</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>19920</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>21800</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>23550</v>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>36800</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>41700</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>46600</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>48100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mini teatro de los Esteros del iberá con Títeres de dedo de animalitos de Los Esteros del Iberá</t>
+          <t>Teatro Castillo con Títeres del Cuento "Príncipe Sapo y su Princesa"</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>19950</v>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>36800</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mini teatro granja con títeres de dedo de La Granja Arcoiris</t>
+          <t>Teatro Ciudad con Títeres de La Familia Monte Espino</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>16300</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>18150</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>19920</v>
-      </c>
-      <c r="J32" s="2" t="n">
-        <v>21800</v>
-      </c>
-      <c r="K32" s="2" t="n">
-        <v>23550</v>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>25350</v>
-      </c>
-      <c r="M32" s="2" t="n">
-        <v>27200</v>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>36800</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>41700</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>46600</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>48100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Miniteatro de Selva Misionera Argentina con Títeres de dedo de la Selva Misionera Argentina</t>
+          <t>Teatro Ciudad con Títeres de Nene y sus Emociones</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>18200</v>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>36800</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>41700</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>46600</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Títeres de dedo Pack x 10 unidades de animalitos</t>
+          <t>Teatro Ciudad con Títeres de nena y sus Emociones</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>18000</v>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>36800</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>41700</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>46600</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Animalitos domésticos</t>
+          <t>Teatro Ciudad con títeres de niños animalitos domésticos</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>7800</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>9600</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>11400</v>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>13200</v>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>36800</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>41700</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>46600</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Caperucita roja</t>
+          <t>Teatro Fondo del mar con Títeres de "La Sirenita"</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>7800</v>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>38200</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Cuento Príncipe Encantado</t>
+          <t>Teatro Granja con Títeres de La Granja</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>10300</v>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>29800</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>32980</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>36200</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>39400</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>46600</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>45800</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>48950</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>52100</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>55300</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Cuento de Hadas</t>
+          <t>Teatro Prehistoria con Títeres de Dinosaurios y Cavernícolas</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>10300</v>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>28900</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>36500</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Títeres de dedo de El Circo Mágico</t>
+          <t>Teatro Selva Misionera Argentina con Títeres de la Selva Misionera</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>10300</v>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>32980</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Heroínas de cuento</t>
+          <t>Teatro Selva con Títeres de la Selva Africana</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="n">
-        <v>10300</v>
-      </c>
-      <c r="H40" s="2" t="n">
-        <v>12700</v>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>17600</v>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>29800</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>32980</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>36200</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>39400</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>46600</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Títeres de dedo de La Familia Monte Espino</t>
+          <t>Teatro bosque con Títeres de Caperucita Roja</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="n">
-        <v>7800</v>
-      </c>
-      <c r="H41" s="2" t="n">
-        <v>9600</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>11400</v>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>13200</v>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>36800</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Títeres de dedo de La Prehistoria</t>
+          <t>Teatro bosque con títeres de Blancanieves y los Siete Enanitos</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n">
-        <v>10825</v>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>34990</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Títeres de dedo de La Sirenita</t>
+          <t>Teatro ciudad con títeres de Superhéroes.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>11450</v>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>36800</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Los Esteros del Iberá</t>
+          <t>Teatro de Títeres Didáctico Clásico para Escuelas y Jardines de Infantes</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>7800</v>
-      </c>
-      <c r="H44" s="2" t="n">
-        <v>9600</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>11400</v>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>13200</v>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>57800</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Los Piratas Siete Mares</t>
+          <t>Teatro de la Época Colonial con Títeres Patrios</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>7800</v>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>29800</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>32980</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>36200</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>39400</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>46600</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>45800</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>48950</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>52100</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>55300</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Los Tres Chanchitos y el lobo</t>
+          <t>Teatro de los Esteros del Iberá Títeres de animales de los Esteros del Iberá</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>36200</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
           <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
-      </c>
-      <c r="C46" s="2" t="n">
-        <v>7800</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Títeres de dedo de Selva Africana</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="n">
-        <v>7800</v>
-      </c>
-      <c r="H47" s="2" t="n">
-        <v>9600</v>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>11400</v>
-      </c>
-      <c r="J47" s="2" t="n">
-        <v>13200</v>
-      </c>
-      <c r="K47" s="2" t="n">
-        <v>15100</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Selva Misionera</t>
+          <t>Mini teatro Barco Pirata con Títeres de dedo de Piratas</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1334,17 +1410,14 @@
           <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
-      <c r="G48" s="2" t="n">
-        <v>7800</v>
-      </c>
-      <c r="H48" s="2" t="n">
-        <v>9600</v>
+      <c r="C48" s="3" t="n">
+        <v>16300</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Superhéroes</t>
+          <t>Mini teatro Bosque con Títeres de dedo del Cuento Blancanieves y los Siete Enanitos</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1352,14 +1425,14 @@
           <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>10300</v>
+      <c r="C49" s="3" t="n">
+        <v>18800</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Títeres de dedo de granja</t>
+          <t>Mini teatro Bosque con Títeres de dedo del Cuento de Caperucita Roja</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1367,26 +1440,14 @@
           <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
-      <c r="G50" s="2" t="n">
-        <v>7800</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>9600</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>11400</v>
-      </c>
-      <c r="J50" s="2" t="n">
-        <v>13200</v>
-      </c>
-      <c r="K50" s="2" t="n">
-        <v>15100</v>
+      <c r="C50" s="3" t="n">
+        <v>16300</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Títeres de dedo del Cuento Blancanieves y los siete enanitos</t>
+          <t>Mini teatro Bosque con Títeres de dedo del cuento Los Tres Chanchitos y el Lobo</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1394,1931 +1455,2483 @@
           <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>10300</v>
+      <c r="C51" s="3" t="n">
+        <v>16300</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Aurora</t>
+          <t>Mini teatro Castillo con Títeres de dedo de Cuento Príncipe Encantado</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>24350</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Bella</t>
+          <t>Mini teatro Castillo con Títeres de dedo de Cuento de Hadas</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>24350</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>18800</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Blancanieves</t>
+          <t>Mini teatro Castillo con Títeres de dedo de Heroínas de Cuento</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>24350</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>18800</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>21250</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>23670</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>26100</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Cenicienta</t>
+          <t>Mini teatro Circo con  Títeres de dedo de Artistas</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>24350</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>18800</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Coqueta</t>
+          <t>Mini teatro Ciudad con Títeres de dedo de  Animalitos Domésticos</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>24350</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>18150</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>19920</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>21800</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>23550</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Deportiva</t>
+          <t>Mini teatro Ciudad con Títeres de dedo de La Familia</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>24350</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>16300</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>18150</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>19920</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>21800</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Folk</t>
+          <t>Mini teatro Ciudad con Títeres de dedo de Superhéroes</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>24350</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>18800</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Jardinera</t>
+          <t>Mini teatro Fondo del Mar con Títeres de dedo de La Sirenita</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>24350</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>19980</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Rapunsel</t>
+          <t>Mini teatro Prehistoria con Títeres de dedo de Dinosaurios y Cavernícolas</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>24350</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>14500</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>16200</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>19360</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Romántica</t>
+          <t>Mini teatro Selva con Títeres de dedo de la Selva Africana</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>24350</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>16300</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>18150</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>19920</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>21800</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>23550</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Sofía</t>
+          <t>Mini teatro de los Esteros del iberá con Títeres de dedo de animalitos de Los Esteros del Iberá</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v>24350</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>19950</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina doctora</t>
+          <t>Mini teatro granja con títeres de dedo de La Granja Arcoiris</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="n">
-        <v>24350</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>16300</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>18150</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>19920</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>21800</v>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>23550</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>25350</v>
+      </c>
+      <c r="M63" s="3" t="n">
+        <v>27200</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Traje de doctora para muñecas</t>
+          <t>Miniteatro de Selva Misionera Argentina con Títeres de dedo de la Selva Misionera Argentina</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>18200</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Traje de jardinera para muñecas</t>
+          <t>Títeres de dedo Pack x 10 unidades de animalitos</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Traje deportivo para muñecas</t>
+          <t>Títeres de dedo de Animalitos domésticos</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>9600</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>11400</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>13200</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Vestido campesino para muñecas</t>
+          <t>Títeres de dedo de Caperucita roja</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>7800</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Vestido coqueta para muñecas</t>
+          <t>Títeres de dedo de Cuento Príncipe Encantado</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>10300</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Vestido de Aurora para muñecas</t>
+          <t>Títeres de dedo de Cuento de Hadas</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>10300</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Vestido de Bella para muñecas</t>
+          <t>Títeres de dedo de El Circo Mágico</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>10300</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Vestido de Blancanieves para muñecas</t>
+          <t>Títeres de dedo de Heroínas de cuento</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>10300</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>12700</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>17600</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Vestido de Cenicienta para muñecas</t>
+          <t>Títeres de dedo de La Familia Monte Espino</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>9600</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>11400</v>
+      </c>
+      <c r="J72" s="3" t="n">
+        <v>13200</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Vestido de Princesa Sofía para muñecas</t>
+          <t>Títeres de dedo de La Prehistoria</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>10825</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Vestido de Rapunzel para muñecas</t>
+          <t>Títeres de dedo de La Sirenita</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>11450</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Vestido romántico para muñecas</t>
+          <t>Títeres de dedo de Los Esteros del Iberá</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="n">
-        <v>8300</v>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>9600</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>11400</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>13200</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Blancanieves y los Siete Enanitos. Títeres de Mano y de Dedo.</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="n">
-        <v>29450</v>
+          <t>Títeres de dedo de Los Piratas Siete Mares</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>7800</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Bolsito Amasando ideas Elefante</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="n">
-        <v>12000</v>
+          <t>Títeres de dedo de Los Tres Chanchitos y el lobo</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>7800</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Bolsito Amasando ideas Espacio</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v>12000</v>
+          <t>Títeres de dedo de Selva Africana</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>9600</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>11400</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>13200</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>15100</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Bolsito Amasando ideas Gato automovilista</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="n">
-        <v>12000</v>
+          <t>Títeres de dedo de Selva Misionera</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>9600</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Bolsito Amasando ideas Pajaritos</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v>12000</v>
+          <t>Títeres de dedo de Superhéroes</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>10300</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Caperucita Roja. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v>20300</v>
+          <t>Títeres de dedo de granja</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>9600</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>11400</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>13200</v>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>15100</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cuento de Hadas. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="n">
-        <v>20300</v>
+          <t>Títeres de dedo del Cuento Blancanieves y los siete enanitos</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>10300</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Cuento de Príncipe Sapo y su Princesa. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="n">
-        <v>20300</v>
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Disfraz de Anna (Frozen)</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="n">
-        <v>24850</v>
+          <t>Bolsito Amasando ideas Elefante</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Disfraz de Araña</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="n">
-        <v>23500</v>
+          <t>Bolsito Amasando ideas Espacio</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Disfraz de Batman</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="n">
-        <v>23500</v>
+          <t>Bolsito Amasando ideas Gato automovilista</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Disfraz de Bella</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="n">
-        <v>23970</v>
+          <t>Bolsito Amasando ideas Pajaritos</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Disfraz de Blancanieves</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="n">
-        <v>24850</v>
+          <t>Valija de Arte Mini Artista, Dinosaurios</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Disfraz de Bombero</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="n">
-        <v>15000</v>
+          <t>Valija de Arte Mini Artista, Haditas</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Disfraz de Capitán América</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="n">
-        <v>23500</v>
+          <t>Valija de Arte Mini Artista, Piratas</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Disfraz de Cebra</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="n">
-        <v>23500</v>
+          <t>Valija de Arte Mini Artista, Ponis</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Disfraz de Cenicienta</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="n">
-        <v>23970</v>
+          <t>Valija de Arte Mini Artista, Sirenitas</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Disfraz de Dinosaurio</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="n">
-        <v>25200</v>
+          <t>Valija de Arte Mini Artista, Superhéroes</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Disfraz de Elsa (Frozen)</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="n">
-        <v>24850</v>
+          <t>Valija de Arte Mis Diseños. Astronautas</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>25850</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Disfraz de Hombre Araña</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="n">
-        <v>18000</v>
+          <t>Valija de Arte Mis Diseños. Cocodrilo en Submarino</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>25850</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Disfraz de Mira K-Pop Demon Hunters</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="n">
-        <v>38500</v>
+          <t>Valija de Arte Mis Diseños. Gato Automovilista</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>25850</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Disfraz de Moana</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="n">
-        <v>24500</v>
+          <t>Valija de Arte Mis Diseños. Monstruos</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>25850</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Disfraz de Mujer Maravilla</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="n">
-        <v>19850</v>
+          <t>Valija de Arte Mis Diseños. Nena con Globos</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>25850</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Disfraz de Pirata</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="n">
-        <v>18000</v>
+          <t>Valija de Arte Mis Diseños. Nena en Hamaca</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>25850</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Disfraz de Policía</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="n">
-        <v>15000</v>
+          <t>Valija de Arte Mis Diseños. Princesa</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>25850</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Disfraz de Princesa Aurora,  La Bella Durmiente</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="n">
-        <v>23970</v>
+          <t>Valija de Arte Mis Diseños. Robots</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>25850</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Disfraz de Rapunzel Encantada</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="n">
-        <v>33300</v>
+          <t>Valija de Arte Mis Diseños. Unicornio</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>25850</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Disfraz de Rumi K-Pop Demon Hunters</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="n">
-        <v>28500</v>
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Disfraz de Rumi K-Pop Demon Hunters (Traje de colores con Chaqueta amarilla)</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="n">
-        <v>51800</v>
+          <t>Bolsito Chef nena</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>11500</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Disfraz de Rumi K-Pop Demon Hunters, con Chaqueta y encanto dorado</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="n">
-        <v>53200</v>
+          <t>Bolsito Chef varón</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>11500</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Disfraz de Sirenita</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="n">
-        <v>22500</v>
+          <t>Bolsito Explorador Jirafas</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>11500</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Disfraz de Superman</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="n">
-        <v>22000</v>
+          <t>Bolsito Explorador África</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>11500</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Disfraz de Tigre</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="n">
-        <v>23500</v>
+          <t>Bolsito Mini Peluquería</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>11500</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Disfraz de Unicornio Mágico</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="n">
-        <v>27400</v>
+          <t>Set de esqueleto y órganos del cuerpo humano para Docentes y Educadores</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>16500</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>El Circo Mágico. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="n">
-        <v>20300</v>
+          <t>Valija de Mini Chef nena</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>21000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>El Pesebre de Navideño. Títeres de Mano.</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="n">
-        <v>41200</v>
+          <t>Valija de Mini Chef varón</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>21000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Globo Pelota Animalitos</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="n">
-        <v>6800</v>
+          <t>Valija de Mini Doctor</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>37500</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Globo Pelota Dinosaurios</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="n">
-        <v>6800</v>
+          <t>Valija de Mini Exploradores</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>24800</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Globo Pelota Gatitos</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="n">
-        <v>6800</v>
+          <t>Valija de Mini Jardineros</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Globo Pelota Haditas</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="n">
-        <v>6800</v>
+          <t>Valija de Mini Maestra</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>28600</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Globo Pelota Monstruos</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="n">
-        <v>6800</v>
+          <t>Valija de Mini Maestro</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>28600</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Globo Pelota Selva</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="n">
-        <v>6800</v>
+          <t>Valija de Mini Spa</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>29800</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Heroínas de Cuentos Clásicos. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="n">
-        <v>15400</v>
-      </c>
-      <c r="G118" s="2" t="n">
-        <v>20300</v>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>25200</v>
-      </c>
-      <c r="I118" s="2" t="n">
-        <v>30200</v>
-      </c>
-      <c r="J118" s="2" t="n">
-        <v>35100</v>
+          <t>Valija de Mini Veterinarios</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>26400</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>La Familia Monte Espino. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="n">
-        <v>20300</v>
-      </c>
-      <c r="H119" s="2" t="n">
-        <v>25200</v>
-      </c>
-      <c r="I119" s="2" t="n">
-        <v>30200</v>
-      </c>
-      <c r="J119" s="2" t="n">
-        <v>35100</v>
-      </c>
-      <c r="K119" s="2" t="n">
-        <v>39960</v>
-      </c>
-      <c r="L119" s="2" t="n">
-        <v>44900</v>
-      </c>
-      <c r="M119" s="2" t="n">
-        <v>54750</v>
+          <t>Valija de Tarde de Mate</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>La Granja Arcoíris. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="n">
-        <v>11850</v>
-      </c>
-      <c r="H120" s="2" t="n">
-        <v>16500</v>
-      </c>
-      <c r="I120" s="2" t="n">
-        <v>19700</v>
-      </c>
-      <c r="J120" s="2" t="n">
-        <v>22860</v>
-      </c>
-      <c r="K120" s="2" t="n">
-        <v>26100</v>
-      </c>
-      <c r="L120" s="2" t="n">
-        <v>29300</v>
-      </c>
-      <c r="M120" s="2" t="n">
-        <v>33200</v>
-      </c>
-      <c r="N120" s="2" t="n">
-        <v>35700</v>
-      </c>
-      <c r="O120" s="2" t="n">
-        <v>38800</v>
+          <t>Valija de Tardes de Té</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>25000</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>La Prehistoria: Dinosaurios y Cavernícolas. Títeres de mano.</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="n">
-        <v>11200</v>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>19960</v>
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>La Selva Africana. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="n">
-        <v>11850</v>
-      </c>
-      <c r="H122" s="2" t="n">
-        <v>16500</v>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>19700</v>
-      </c>
-      <c r="J122" s="2" t="n">
-        <v>22860</v>
-      </c>
-      <c r="K122" s="2" t="n">
-        <v>26100</v>
+          <t>Disfraz de Anna (Frozen)</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>24850</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>La Selva Misionera Argentina. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="n">
-        <v>19000</v>
+          <t>Disfraz de Bella</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>23970</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>La Sirenita. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="n">
-        <v>25200</v>
+          <t>Disfraz de Blancanieves</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>24850</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Las Emociones. Títeres de Mano de Nena</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="n">
-        <v>30200</v>
+          <t>Disfraz de Cenicienta</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>23970</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Las Emociones. Títeres de Mano de Nene</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="n">
-        <v>30200</v>
+          <t>Disfraz de Elsa (Frozen)</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>24850</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Libro para bebé "Coral"</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="n">
-        <v>8400</v>
+          <t>Disfraz de Mira K-Pop Demon Hunters</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v>38500</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Libro para bebé "Cosquillitas"</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="n">
-        <v>8400</v>
+          <t>Disfraz de Moana</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>24500</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Libro para bebé "Mariposas"</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="n">
-        <v>8400</v>
+          <t>Disfraz de Mujer Maravilla</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>19850</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Los 3 Chanchitos y el Lobo Feroz . Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="n">
-        <v>11850</v>
+          <t>Disfraz de Princesa Aurora,  La Bella Durmiente</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>23970</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Los Esteros del Iberá. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="n">
-        <v>23200</v>
+          <t>Disfraz de Rapunzel Encantada</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>33300</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Los Piratas Siete Mares. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="n">
-        <v>20300</v>
+          <t>Disfraz de Rumi K-Pop Demon Hunters</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>28500</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Manta para bebé "Animalitos de la Selva"</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="n">
-        <v>15600</v>
+          <t>Disfraz de Rumi K-Pop Demon Hunters (Traje de colores con Chaqueta amarilla)</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>51800</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Manta para bebé "La Ciudad"</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="n">
-        <v>15600</v>
+          <t>Disfraz de Rumi K-Pop Demon Hunters, con Chaqueta y encanto dorado</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>53200</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Manta para bebé "Mininos"</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="n">
-        <v>15600</v>
+          <t>Disfraz de Sirenita</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>22500</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Mis amigos los animalitos domésticos . Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="n">
-        <v>16500</v>
-      </c>
-      <c r="J136" s="2" t="n">
-        <v>26350</v>
+          <t>Disfraz de Unicornio Mágico</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>27400</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Navidad. Títeres de Mano.</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="n">
-        <v>11200</v>
+          <t>Disfraz de Zoey  K-Pop Demon Hunters</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Pelota de Trapo  Animalitos</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="n">
-        <v>15950</v>
+          <t>Tutú de Bailarina Unicornio</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>23200</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Pelota de Trapo  Dinosaurios</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="n">
-        <v>15950</v>
+          <t>Tutú de bailarina</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Pelota de Trapo Gatitos</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="n">
-        <v>15950</v>
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENES</t>
+        </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Pelota de Trapo Selva</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="n">
-        <v>15950</v>
+          <t>Disfraz de Batman</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENES</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Pulpitos Reversibles con dos emociones (alegre/ enojado)</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="n">
-        <v>7500</v>
+          <t>Disfraz de Bombero</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENES</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Rayuela de tela para aprender los números jugando</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="n">
-        <v>24500</v>
+          <t>Disfraz de Capitán América</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENES</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Superhéroes. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="n">
-        <v>20300</v>
+          <t>Disfraz de Hombre Araña</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENES</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Teatro "El Circo Mágico" con Títeres de Artistas</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="n">
-        <v>36800</v>
+          <t>Disfraz de Pirata</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENES</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Teatro Barco con Títeres de Los Piratas de los Siete Mares.</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="n">
-        <v>36800</v>
+          <t>Disfraz de Policía</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENES</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Teatro Bosque con Títeres del cuento "Los tres Chanchitos y el Lobo Feroz"</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="n">
-        <v>29800</v>
+          <t>Disfraz de Superman</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENES</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="n">
+        <v>22000</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Teatro Castillo con Títeres de Cuento de Hadas</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="n">
-        <v>36800</v>
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>DISFRACES DE ANIMALITOS</t>
+        </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Teatro Castillo con Títeres de Heroínas de Cuentos Clásicos.</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="n">
-        <v>36800</v>
-      </c>
-      <c r="H149" s="2" t="n">
-        <v>41700</v>
-      </c>
-      <c r="I149" s="2" t="n">
-        <v>46600</v>
-      </c>
-      <c r="J149" s="2" t="n">
-        <v>48100</v>
+          <t>Disfraz de Araña</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>DISFRACES DE ANIMALITOS</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Teatro Castillo con Títeres del Cuento "Príncipe Sapo y su Princesa"</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="n">
-        <v>36800</v>
+          <t>Disfraz de Cebra</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>DISFRACES DE ANIMALITOS</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con Títeres de La Familia Monte Espino</t>
-        </is>
-      </c>
-      <c r="G151" s="2" t="n">
-        <v>36800</v>
-      </c>
-      <c r="H151" s="2" t="n">
-        <v>41700</v>
-      </c>
-      <c r="I151" s="2" t="n">
-        <v>46600</v>
-      </c>
-      <c r="J151" s="2" t="n">
-        <v>48100</v>
+          <t>Disfraz de Dinosaurio</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>DISFRACES DE ANIMALITOS</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="n">
+        <v>25200</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con Títeres de Nene y sus Emociones</t>
-        </is>
-      </c>
-      <c r="G152" s="2" t="n">
-        <v>36800</v>
-      </c>
-      <c r="H152" s="2" t="n">
-        <v>41700</v>
-      </c>
-      <c r="I152" s="2" t="n">
-        <v>46600</v>
+          <t>Disfraz de Tigre</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>DISFRACES DE ANIMALITOS</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Teatro Ciudad con Títeres de nena y sus Emociones</t>
-        </is>
-      </c>
-      <c r="G153" s="2" t="n">
-        <v>36800</v>
-      </c>
-      <c r="H153" s="2" t="n">
-        <v>41700</v>
-      </c>
-      <c r="I153" s="2" t="n">
-        <v>46600</v>
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con títeres de niños animalitos domésticos</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="n">
-        <v>36800</v>
-      </c>
-      <c r="H154" s="2" t="n">
-        <v>41700</v>
-      </c>
-      <c r="I154" s="2" t="n">
-        <v>46600</v>
+          <t>Caramelera Calabaza</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Teatro Fondo del mar con Títeres de "La Sirenita"</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="n">
-        <v>38200</v>
+          <t>Disfraz de Araña</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Teatro Granja con Títeres de La Granja</t>
-        </is>
-      </c>
-      <c r="G156" s="2" t="n">
-        <v>29800</v>
-      </c>
-      <c r="H156" s="2" t="n">
-        <v>32980</v>
-      </c>
-      <c r="I156" s="2" t="n">
-        <v>36200</v>
-      </c>
-      <c r="J156" s="2" t="n">
-        <v>39400</v>
-      </c>
-      <c r="K156" s="2" t="n">
-        <v>46600</v>
-      </c>
-      <c r="L156" s="2" t="n">
-        <v>45800</v>
-      </c>
-      <c r="M156" s="2" t="n">
-        <v>48950</v>
-      </c>
-      <c r="N156" s="2" t="n">
-        <v>52100</v>
-      </c>
-      <c r="O156" s="2" t="n">
-        <v>55300</v>
+          <t>Disfraz de Brujita Fuxia</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="n">
+        <v>25500</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Teatro Prehistoria con Títeres de Dinosaurios y Cavernícolas</t>
-        </is>
-      </c>
-      <c r="F157" s="2" t="n">
-        <v>28900</v>
-      </c>
-      <c r="H157" s="2" t="n">
-        <v>36500</v>
+          <t>Disfraz de Brujita Naranja</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="n">
+        <v>25500</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Teatro Selva Misionera Argentina con Títeres de la Selva Misionera</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="n">
-        <v>32980</v>
+          <t>Disfraz de Brujita Verde</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>25500</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Teatro Selva con Títeres de la Selva Africana</t>
-        </is>
-      </c>
-      <c r="G159" s="2" t="n">
-        <v>29800</v>
-      </c>
-      <c r="H159" s="2" t="n">
-        <v>32980</v>
-      </c>
-      <c r="I159" s="2" t="n">
-        <v>36200</v>
-      </c>
-      <c r="J159" s="2" t="n">
-        <v>39400</v>
-      </c>
-      <c r="K159" s="2" t="n">
-        <v>46600</v>
+          <t>Disfraz de Brujita Violeta</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="n">
+        <v>25500</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Teatro bosque con Títeres de Caperucita Roja</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="n">
-        <v>36800</v>
+          <t>Disfraz de Calabaza</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Teatro bosque con títeres de Blancanieves y los Siete Enanitos</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="n">
-        <v>34990</v>
+          <t>Disfraz de Esqueleto</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="n">
+        <v>25000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Teatro ciudad con títeres de Superhéroes.</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="n">
-        <v>36800</v>
+          <t>Disfraz de Merlina</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>32000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Teatro de Títeres Didáctico Clásico para Escuelas y Jardines de Infantes</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="n">
-        <v>57800</v>
+          <t>Disfraz de Vampira</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>25300</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Teatro de la Época Colonial con Títeres Patrios</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="n">
-        <v>29800</v>
-      </c>
-      <c r="H164" s="2" t="n">
-        <v>32980</v>
-      </c>
-      <c r="I164" s="2" t="n">
-        <v>36200</v>
-      </c>
-      <c r="J164" s="2" t="n">
-        <v>39400</v>
-      </c>
-      <c r="K164" s="2" t="n">
-        <v>46600</v>
-      </c>
-      <c r="L164" s="2" t="n">
-        <v>45800</v>
-      </c>
-      <c r="M164" s="2" t="n">
-        <v>48950</v>
-      </c>
-      <c r="N164" s="2" t="n">
-        <v>52100</v>
-      </c>
-      <c r="O164" s="2" t="n">
-        <v>55300</v>
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Teatro de los Esteros del Iberá Títeres de animales de los Esteros del Iberá</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="n">
-        <v>36200</v>
+          <t>Cesto para juguetes Cactus</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>22900</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Tutú de Bailarina Unicornio</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="n">
-        <v>23200</v>
+          <t>Cesto para juguetes Cebra y Jirafa</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="n">
+        <v>22900</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Tutú de bailarina</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="n">
-        <v>19500</v>
+          <t>Cesto para juguetes Gatitos</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>22900</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Títeres Patrios. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="n">
-        <v>11850</v>
-      </c>
-      <c r="H168" s="2" t="n">
-        <v>16500</v>
-      </c>
-      <c r="I168" s="2" t="n">
-        <v>19700</v>
-      </c>
-      <c r="J168" s="2" t="n">
-        <v>22860</v>
-      </c>
-      <c r="K168" s="2" t="n">
-        <v>26100</v>
-      </c>
-      <c r="L168" s="2" t="n">
-        <v>29300</v>
-      </c>
-      <c r="M168" s="2" t="n">
-        <v>33200</v>
-      </c>
-      <c r="N168" s="2" t="n">
-        <v>35700</v>
-      </c>
-      <c r="O168" s="2" t="n">
-        <v>38800</v>
+          <t>Cesto para juguetes Indi</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="n">
+        <v>22900</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Astronautas</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="n">
-        <v>25850</v>
+          <t>Globo Pelota Animalitos</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="n">
+        <v>6800</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Cocodrilo en Submarino</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="n">
-        <v>25850</v>
+          <t>Globo Pelota Dinosaurios</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="n">
+        <v>6800</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Gato Automovilista</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="n">
-        <v>25850</v>
+          <t>Globo Pelota Gatitos</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="n">
+        <v>6800</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Monstruos</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="n">
-        <v>25850</v>
+          <t>Globo Pelota Haditas</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="n">
+        <v>6800</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Nena con Globos</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="n">
-        <v>25850</v>
+          <t>Globo Pelota Monstruos</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="n">
+        <v>6800</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Nena en Hamaca</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="n">
-        <v>25850</v>
+          <t>Globo Pelota Selva</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="n">
+        <v>6800</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Princesa</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="n">
-        <v>25850</v>
+          <t>Libro para bebé "Coral"</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="n">
+        <v>8400</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Robots</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="n">
-        <v>25850</v>
+          <t>Libro para bebé "Cosquillitas"</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="n">
+        <v>8400</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Unicornio</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="n">
-        <v>25850</v>
+          <t>Libro para bebé "Mariposas"</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="n">
+        <v>8400</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Dinosaurios</t>
+          <t>Manta para bebé "Animalitos de la Selva"</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="n">
-        <v>19500</v>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="n">
+        <v>15600</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Haditas</t>
+          <t>Manta para bebé "La Ciudad"</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="n">
-        <v>19500</v>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="n">
+        <v>15600</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Piratas</t>
+          <t>Manta para bebé "Mininos"</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="n">
-        <v>19500</v>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="n">
+        <v>15600</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Ponis</t>
+          <t>Pelota de Trapo  Animalitos</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="n">
-        <v>19500</v>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="n">
+        <v>15950</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Sirenitas</t>
+          <t>Pelota de Trapo  Dinosaurios</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="n">
-        <v>19500</v>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="n">
+        <v>15950</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Superhéroes</t>
+          <t>Pelota de Trapo Gatitos</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="n">
-        <v>19500</v>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="n">
+        <v>15950</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Bolsito Chef nena</t>
+          <t>Pelota de Trapo Selva</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="n">
-        <v>11500</v>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="n">
+        <v>15950</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Bolsito Chef varón</t>
+          <t>Pulpitos Reversibles con dos emociones (alegre/ enojado)</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="n">
-        <v>11500</v>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="n">
+        <v>7500</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Bolsito Explorador Jirafas</t>
+          <t>Rayuela de tela para aprender los números jugando</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="n">
-        <v>11500</v>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="n">
+        <v>24500</v>
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Bolsito Explorador África</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="n">
-        <v>11500</v>
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Bolsito Mini Peluquería</t>
+          <t>Muñeca Piccolina Aurora</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="n">
-        <v>11500</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Set de esqueleto y órganos del cuerpo humano para Docentes y Educadores</t>
+          <t>Muñeca Piccolina Bella</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C189" s="2" t="n">
-        <v>16500</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Valija de Mini Chef nena</t>
+          <t>Muñeca Piccolina Blancanieves</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C190" s="2" t="n">
-        <v>21000</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Valija de Mini Chef varón</t>
+          <t>Muñeca Piccolina Cenicienta</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C191" s="2" t="n">
-        <v>21000</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Valija de Mini Doctor</t>
+          <t>Muñeca Piccolina Coqueta</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C192" s="2" t="n">
-        <v>37500</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Valija de Mini Exploradores</t>
+          <t>Muñeca Piccolina Deportiva</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="n">
-        <v>24800</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Valija de Mini Jardineros</t>
+          <t>Muñeca Piccolina Folk</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C194" s="2" t="n">
-        <v>23500</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Valija de Mini Maestra</t>
+          <t>Muñeca Piccolina Jardinera</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C195" s="2" t="n">
-        <v>28600</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Valija de Mini Maestro</t>
+          <t>Muñeca Piccolina Rapunsel</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C196" s="2" t="n">
-        <v>28600</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Valija de Mini Spa</t>
+          <t>Muñeca Piccolina Romántica</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C197" s="2" t="n">
-        <v>29800</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C197" s="3" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Valija de Mini Veterinarios</t>
+          <t>Muñeca Piccolina Sofía</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C198" s="2" t="n">
-        <v>26400</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C198" s="3" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Valija de Tarde de Mate</t>
+          <t>Muñeca Piccolina doctora</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C199" s="2" t="n">
-        <v>19500</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C199" s="3" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Valija de Tardes de Té</t>
+          <t>Traje de doctora para muñecas</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="n">
-        <v>25000</v>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C200" s="3" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Traje de jardinera para muñecas</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C201" s="3" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Traje deportivo para muñecas</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C202" s="3" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Vestido campesino para muñecas</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C203" s="3" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Vestido coqueta para muñecas</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C204" s="3" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Vestido de Aurora para muñecas</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C205" s="3" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Vestido de Bella para muñecas</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C206" s="3" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Vestido de Blancanieves para muñecas</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C207" s="3" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Vestido de Cenicienta para muñecas</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C208" s="3" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Vestido de Princesa Sofía para muñecas</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Vestido de Rapunzel para muñecas</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Vestido romántico para muñecas</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="n">
+        <v>8300</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A83:O83"/>
+    <mergeCell ref="A148:O148"/>
+    <mergeCell ref="A25:O25"/>
+    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A187:O187"/>
+    <mergeCell ref="A121:O121"/>
+    <mergeCell ref="A47:O47"/>
+    <mergeCell ref="A103:O103"/>
+    <mergeCell ref="A164:O164"/>
+    <mergeCell ref="A153:O153"/>
+    <mergeCell ref="A140:O140"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/lista_precios_clientes.xlsx
+++ b/lista_precios_clientes.xlsx
@@ -73,7 +73,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -441,3496 +441,3496 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O211"/>
+  <dimension ref="A4:O214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Categoría</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Set con 1 títere</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Set con 2 títeres</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Set con 3 títeres</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Set con 4 títeres</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Set con 5 títeres</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>Set con 6 títeres</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>Set con 7 títeres</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>Set con 8 títeres</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>Set con 9 títeres</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>Set con 10 títeres</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>Set con 11 títeres</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>Set con 12 títeres</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
         <is>
           <t>Precio mayorista</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Set con 1 títere</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Set con 2 títeres</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Set con 3 títeres</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Set con 4 títeres</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Set con 5 títeres</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Set con 6 títeres</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Set con 7 títeres</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Set con 8 títeres</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Set con 9 títeres</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Set con 10 títeres</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Set con 11 títeres</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Set con 12 títeres</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>TÍTERES DE MANO</t>
         </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Blancanieves y los Siete Enanitos. Títeres de Mano y de Dedo.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>29450</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Caperucita Roja. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>20300</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cuento de Hadas. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>20300</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cuento de Príncipe Sapo y su Princesa. Títeres de Mano</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>20300</v>
+          <t>Blancanieves y los Siete Enanitos. Títeres de Mano y de Dedo.</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>29450</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>El Circo Mágico. Títeres de Mano</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
+          <t>Caperucita Roja. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="n">
         <v>20300</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>El Pesebre de Navideño. Títeres de Mano.</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>41200</v>
+          <t>Cuento de Hadas. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>20300</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Heroínas de Cuentos Clásicos. Títeres de Mano</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>15400</v>
-      </c>
-      <c r="G9" s="3" t="n">
+          <t>Cuento de Príncipe Sapo y su Princesa. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="n">
         <v>20300</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>25200</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>30200</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>35100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>La Familia Monte Espino. Títeres de Mano</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="n">
+          <t>El Circo Mágico. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="n">
         <v>20300</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>25200</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>30200</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>35100</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>39960</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>44900</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>54750</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>La Granja Arcoíris. Títeres de Mano</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>11850</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>16500</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>19700</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>22860</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>26100</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>29300</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>33200</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>35700</v>
+          <t>El Pesebre de Navideño. Títeres de Mano.</t>
+        </is>
       </c>
       <c r="O11" s="3" t="n">
-        <v>38800</v>
+        <v>41200</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>La Prehistoria: Dinosaurios y Cavernícolas. Títeres de mano.</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
+          <t>Heroínas de Cuentos Clásicos. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>15400</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>11200</v>
+        <v>20300</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>25200</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>19960</v>
+        <v>30200</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>35100</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>La Selva Africana. Títeres de Mano</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
+          <t>La Familia Monte Espino. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>20300</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>11850</v>
+        <v>25200</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>16500</v>
+        <v>30200</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>19700</v>
+        <v>35100</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>22860</v>
+        <v>39960</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>26100</v>
+        <v>44900</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>54750</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>La Selva Misionera Argentina. Títeres de Mano</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>19000</v>
+          <t>La Granja Arcoíris. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>11850</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>16500</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>19700</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>22860</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>26100</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>29300</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>33200</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>35700</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>38800</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>La Sirenita. Títeres de Mano</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>25200</v>
+          <t>La Prehistoria: Dinosaurios y Cavernícolas. Títeres de mano.</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>11200</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>19960</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Las Emociones. Títeres de Mano de Nena</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>30200</v>
+          <t>La Selva Africana. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>11850</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>16500</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>19700</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>22860</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>26100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Las Emociones. Títeres de Mano de Nene</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>30200</v>
+          <t>La Selva Misionera Argentina. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>19000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Los 3 Chanchitos y el Lobo Feroz . Títeres de Mano</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>11850</v>
+          <t>La Sirenita. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>25200</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Los Esteros del Iberá. Títeres de Mano</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>23200</v>
+          <t>Las Emociones. Títeres de Mano de Nena</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>30200</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Los Piratas Siete Mares. Títeres de Mano</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>20300</v>
+          <t>Las Emociones. Títeres de Mano de Nene</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>30200</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mis amigos los animalitos domésticos . Títeres de Mano</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>16500</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>26350</v>
+          <t>Los 3 Chanchitos y el Lobo Feroz . Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>11850</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Navidad. Títeres de Mano.</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>11200</v>
+          <t>Los Esteros del Iberá. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>23200</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Superhéroes. Títeres de Mano</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="n">
+          <t>Los Piratas Siete Mares. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="n">
         <v>20300</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Títeres Patrios. Títeres de Mano</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>Mis amigos los animalitos domésticos . Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>16500</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>26350</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>TÍTERES DE MANO</t>
         </is>
       </c>
-      <c r="G24" s="3" t="n">
-        <v>11850</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>16500</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>19700</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>22860</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>26100</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>29300</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>33200</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>35700</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>38800</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Navidad. Títeres de Mano.</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>11200</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Teatro "El Circo Mágico" con Títeres de Artistas</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>36800</v>
+          <t>Superhéroes. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>20300</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Teatro Barco con Títeres de Los Piratas de los Siete Mares.</t>
+          <t>TÍTERES DE MANO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>Títeres Patrios. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>11850</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>16500</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>19700</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>22860</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>26100</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>29300</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>33200</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>35700</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>38800</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t>TEATROS CON TÍTERES</t>
         </is>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>36800</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Teatro Bosque con Títeres del cuento "Los tres Chanchitos y el Lobo Feroz"</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>29800</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Teatro Castillo con Títeres de Cuento de Hadas</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="n">
+          <t>Teatro "El Circo Mágico" con Títeres de Artistas</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="n">
         <v>36800</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Teatro Castillo con Títeres de Heroínas de Cuentos Clásicos.</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="n">
+          <t>Teatro Barco con Títeres de Los Piratas de los Siete Mares.</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="n">
         <v>36800</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>41700</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>46600</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>48100</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Teatro Castillo con Títeres del Cuento "Príncipe Sapo y su Princesa"</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>36800</v>
+          <t>Teatro Bosque con Títeres del cuento "Los tres Chanchitos y el Lobo Feroz"</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>29800</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con Títeres de La Familia Monte Espino</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="n">
+          <t>Teatro Castillo con Títeres de Cuento de Hadas</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="n">
         <v>36800</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>41700</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>46600</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>48100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con Títeres de Nene y sus Emociones</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
+          <t>Teatro Castillo con Títeres de Heroínas de Cuentos Clásicos.</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>36800</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>36800</v>
+        <v>41700</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>41700</v>
+        <v>46600</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>46600</v>
+        <v>48100</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con Títeres de nena y sus Emociones</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="n">
+          <t>Teatro Castillo con Títeres del Cuento "Príncipe Sapo y su Princesa"</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="n">
         <v>36800</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>41700</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>46600</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con títeres de niños animalitos domésticos</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
+          <t>Teatro Ciudad con Títeres de La Familia Monte Espino</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>36800</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>36800</v>
+        <v>41700</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>41700</v>
+        <v>46600</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>46600</v>
+        <v>48100</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Teatro Fondo del mar con Títeres de "La Sirenita"</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>38200</v>
+          <t>Teatro Ciudad con Títeres de Nene y sus Emociones</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>36800</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>41700</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>46600</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Teatro Granja con Títeres de La Granja</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
+          <t>Teatro Ciudad con Títeres de nena y sus Emociones</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>36800</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>29800</v>
+        <v>41700</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>32980</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>36200</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>39400</v>
-      </c>
-      <c r="K37" s="3" t="n">
         <v>46600</v>
-      </c>
-      <c r="L37" s="3" t="n">
-        <v>45800</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>48950</v>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>52100</v>
-      </c>
-      <c r="O37" s="3" t="n">
-        <v>55300</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Teatro Prehistoria con Títeres de Dinosaurios y Cavernícolas</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TEATROS CON TÍTERES</t>
+          <t>Teatro Ciudad con títeres de niños animalitos domésticos</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>28900</v>
+        <v>36800</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>41700</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>36500</v>
+        <v>46600</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Teatro Selva Misionera Argentina con Títeres de la Selva Misionera</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>32980</v>
+          <t>Teatro Fondo del mar con Títeres de "La Sirenita"</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>38200</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Teatro Selva con Títeres de la Selva Africana</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
+          <t>Teatro Granja con Títeres de La Granja</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>29800</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>29800</v>
+        <v>32980</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>32980</v>
+        <v>36200</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>36200</v>
+        <v>39400</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>39400</v>
+        <v>46600</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>46600</v>
+        <v>45800</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>48950</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>52100</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>55300</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Teatro bosque con Títeres de Caperucita Roja</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>36800</v>
+          <t>Teatro Prehistoria con Títeres de Dinosaurios y Cavernícolas</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>28900</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>36500</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Teatro bosque con títeres de Blancanieves y los Siete Enanitos</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>34990</v>
+          <t>Teatro Selva Misionera Argentina con Títeres de la Selva Misionera</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>32980</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Teatro ciudad con títeres de Superhéroes.</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>36800</v>
+          <t>Teatro Selva con Títeres de la Selva Africana</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>29800</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>32980</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>36200</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>39400</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>46600</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Teatro de Títeres Didáctico Clásico para Escuelas y Jardines de Infantes</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>57800</v>
+          <t>Teatro bosque con Títeres de Caperucita Roja</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>36800</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Teatro de la Época Colonial con Títeres Patrios</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>29800</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>32980</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>36200</v>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v>39400</v>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>46600</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>45800</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>48950</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>52100</v>
+          <t>Teatro bosque con títeres de Blancanieves y los Siete Enanitos</t>
+        </is>
       </c>
       <c r="O45" s="3" t="n">
-        <v>55300</v>
+        <v>34990</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Teatro de los Esteros del Iberá Títeres de animales de los Esteros del Iberá</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>Teatro ciudad con títeres de Superhéroes.</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>36800</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n">
-        <v>36200</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Teatro de Títeres Didáctico Clásico para Escuelas y Jardines de Infantes</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>57800</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mini teatro Barco Pirata con Títeres de dedo de Piratas</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v>16300</v>
+          <t>Teatro de la Época Colonial con Títeres Patrios</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>29800</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>32980</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>36200</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>39400</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>46600</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>45800</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>48950</v>
+      </c>
+      <c r="M48" s="3" t="n">
+        <v>52100</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>55300</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mini teatro Bosque con Títeres de dedo del Cuento Blancanieves y los Siete Enanitos</t>
+          <t>TEATROS CON TÍTERES</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>Teatro de los Esteros del Iberá Títeres de animales de los Esteros del Iberá</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>36200</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>18800</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Mini teatro Bosque con Títeres de dedo del Cuento de Caperucita Roja</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="n">
-        <v>16300</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mini teatro Bosque con Títeres de dedo del cuento Los Tres Chanchitos y el Lobo</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="n">
+          <t>Mini teatro Barco Pirata con Títeres de dedo de Piratas</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="n">
         <v>16300</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Mini teatro Castillo con Títeres de dedo de Cuento Príncipe Encantado</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>18000</v>
+          <t>Mini teatro Bosque con Títeres de dedo del Cuento Blancanieves y los Siete Enanitos</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="n">
+        <v>18800</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mini teatro Castillo con Títeres de dedo de Cuento de Hadas</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>18800</v>
+          <t>Mini teatro Bosque con Títeres de dedo del Cuento de Caperucita Roja</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>16300</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mini teatro Castillo con Títeres de dedo de Heroínas de Cuento</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>18800</v>
-      </c>
-      <c r="H54" s="3" t="n">
-        <v>21250</v>
-      </c>
-      <c r="I54" s="3" t="n">
-        <v>23670</v>
-      </c>
-      <c r="J54" s="3" t="n">
-        <v>26100</v>
+          <t>Mini teatro Bosque con Títeres de dedo del cuento Los Tres Chanchitos y el Lobo</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>16300</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mini teatro Circo con  Títeres de dedo de Artistas</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>18800</v>
+          <t>Mini teatro Castillo con Títeres de dedo de Cuento Príncipe Encantado</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mini teatro Ciudad con Títeres de dedo de  Animalitos Domésticos</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="n">
-        <v>18150</v>
-      </c>
-      <c r="I56" s="3" t="n">
-        <v>19920</v>
-      </c>
-      <c r="J56" s="3" t="n">
-        <v>21800</v>
-      </c>
-      <c r="K56" s="3" t="n">
-        <v>23550</v>
+          <t>Mini teatro Castillo con Títeres de dedo de Cuento de Hadas</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="n">
+        <v>18800</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Mini teatro Ciudad con Títeres de dedo de La Familia</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
+          <t>Mini teatro Castillo con Títeres de dedo de Heroínas de Cuento</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>18800</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>16300</v>
+        <v>21250</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>18150</v>
+        <v>23670</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>19920</v>
-      </c>
-      <c r="J57" s="3" t="n">
-        <v>21800</v>
+        <v>26100</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mini teatro Ciudad con Títeres de dedo de Superhéroes</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="n">
+          <t>Mini teatro Circo con  Títeres de dedo de Artistas</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="n">
         <v>18800</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mini teatro Fondo del Mar con Títeres de dedo de La Sirenita</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="n">
-        <v>19980</v>
+          <t>Mini teatro Ciudad con Títeres de dedo de  Animalitos Domésticos</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>18150</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>19920</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>21800</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>23550</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Mini teatro Prehistoria con Títeres de dedo de Dinosaurios y Cavernícolas</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+          <t>Mini teatro Ciudad con Títeres de dedo de La Familia</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>14500</v>
+        <v>16300</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>16200</v>
+        <v>18150</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>19360</v>
+        <v>19920</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>21800</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Mini teatro Selva con Títeres de dedo de la Selva Africana</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="n">
-        <v>16300</v>
-      </c>
-      <c r="H61" s="3" t="n">
-        <v>18150</v>
-      </c>
-      <c r="I61" s="3" t="n">
-        <v>19920</v>
-      </c>
-      <c r="J61" s="3" t="n">
-        <v>21800</v>
-      </c>
-      <c r="K61" s="3" t="n">
-        <v>23550</v>
+          <t>Mini teatro Ciudad con Títeres de dedo de Superhéroes</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>18800</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mini teatro de los Esteros del iberá con Títeres de dedo de animalitos de Los Esteros del Iberá</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="n">
-        <v>19950</v>
+          <t>Mini teatro Fondo del Mar con Títeres de dedo de La Sirenita</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="n">
+        <v>19980</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mini teatro granja con títeres de dedo de La Granja Arcoiris</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
+          <t>Mini teatro Prehistoria con Títeres de dedo de Dinosaurios y Cavernícolas</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>14500</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>16200</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>16300</v>
-      </c>
-      <c r="H63" s="3" t="n">
-        <v>18150</v>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>19920</v>
-      </c>
-      <c r="J63" s="3" t="n">
-        <v>21800</v>
-      </c>
-      <c r="K63" s="3" t="n">
-        <v>23550</v>
-      </c>
-      <c r="L63" s="3" t="n">
-        <v>25350</v>
-      </c>
-      <c r="M63" s="3" t="n">
-        <v>27200</v>
+        <v>19360</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Miniteatro de Selva Misionera Argentina con Títeres de dedo de la Selva Misionera Argentina</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="n">
-        <v>18200</v>
+          <t>Mini teatro Selva con Títeres de dedo de la Selva Africana</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>16300</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>18150</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>19920</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>21800</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>23550</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Títeres de dedo Pack x 10 unidades de animalitos</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="n">
-        <v>18000</v>
+          <t>Mini teatro de los Esteros del iberá con Títeres de dedo de animalitos de Los Esteros del Iberá</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="n">
+        <v>19950</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Animalitos domésticos</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
+          <t>Mini teatro granja con títeres de dedo de La Granja Arcoiris</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>16300</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>7800</v>
+        <v>18150</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>9600</v>
+        <v>19920</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>11400</v>
+        <v>21800</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>13200</v>
+        <v>23550</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>25350</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>27200</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Caperucita roja</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>7800</v>
+          <t>Miniteatro de Selva Misionera Argentina con Títeres de dedo de la Selva Misionera Argentina</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="n">
+        <v>18200</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Cuento Príncipe Encantado</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="n">
-        <v>10300</v>
+          <t>Títeres de dedo Pack x 10 unidades de animalitos</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Cuento de Hadas</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="n">
-        <v>10300</v>
+          <t>Títeres de dedo de Animalitos domésticos</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>9600</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>11400</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>13200</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Títeres de dedo de El Circo Mágico</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="n">
-        <v>10300</v>
+          <t>Títeres de dedo de Caperucita roja</t>
+        </is>
+      </c>
+      <c r="O70" s="3" t="n">
+        <v>7800</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Heroínas de cuento</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="n">
+          <t>Títeres de dedo de Cuento Príncipe Encantado</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="n">
         <v>10300</v>
-      </c>
-      <c r="H71" s="3" t="n">
-        <v>12700</v>
-      </c>
-      <c r="J71" s="3" t="n">
-        <v>17600</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Títeres de dedo de La Familia Monte Espino</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="n">
-        <v>7800</v>
-      </c>
-      <c r="H72" s="3" t="n">
-        <v>9600</v>
-      </c>
-      <c r="I72" s="3" t="n">
-        <v>11400</v>
-      </c>
-      <c r="J72" s="3" t="n">
-        <v>13200</v>
+          <t>Títeres de dedo de Cuento de Hadas</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="n">
+        <v>10300</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Títeres de dedo de La Prehistoria</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="n">
-        <v>10825</v>
+          <t>Títeres de dedo de El Circo Mágico</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="n">
+        <v>10300</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Títeres de dedo de La Sirenita</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="n">
-        <v>11450</v>
+          <t>Títeres de dedo de Heroínas de cuento</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>10300</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>12700</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>17600</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Los Esteros del Iberá</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
+          <t>Títeres de dedo de La Familia Monte Espino</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>7800</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>7800</v>
+        <v>9600</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>9600</v>
+        <v>11400</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>11400</v>
-      </c>
-      <c r="J75" s="3" t="n">
         <v>13200</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Los Piratas Siete Mares</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="n">
-        <v>7800</v>
+          <t>Títeres de dedo de La Prehistoria</t>
+        </is>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>10825</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Los Tres Chanchitos y el lobo</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="n">
-        <v>7800</v>
+          <t>Títeres de dedo de La Sirenita</t>
+        </is>
+      </c>
+      <c r="O77" s="3" t="n">
+        <v>11450</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Selva Africana</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
+          <t>Títeres de dedo de Los Esteros del Iberá</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>7800</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>7800</v>
+        <v>9600</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>9600</v>
+        <v>11400</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>11400</v>
-      </c>
-      <c r="J78" s="3" t="n">
         <v>13200</v>
-      </c>
-      <c r="K78" s="3" t="n">
-        <v>15100</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Selva Misionera</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="n">
+          <t>Títeres de dedo de Los Piratas Siete Mares</t>
+        </is>
+      </c>
+      <c r="O79" s="3" t="n">
         <v>7800</v>
-      </c>
-      <c r="H79" s="3" t="n">
-        <v>9600</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Superhéroes</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="n">
-        <v>10300</v>
+          <t>Títeres de dedo de Los Tres Chanchitos y el lobo</t>
+        </is>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>7800</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Títeres de dedo de granja</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
+          <t>Títeres de dedo de Selva Africana</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>7800</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>7800</v>
+        <v>9600</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>9600</v>
+        <v>11400</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>11400</v>
+        <v>13200</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>13200</v>
-      </c>
-      <c r="K81" s="3" t="n">
         <v>15100</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Títeres de dedo del Cuento Blancanieves y los siete enanitos</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
+          <t>Títeres de dedo de Selva Misionera</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
-      <c r="C82" s="3" t="n">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Títeres de dedo de Superhéroes</t>
+        </is>
+      </c>
+      <c r="O83" s="3" t="n">
         <v>10300</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Bolsito Amasando ideas Elefante</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="n">
-        <v>12000</v>
+          <t>Títeres de dedo de granja</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>9600</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>11400</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>13200</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>15100</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Bolsito Amasando ideas Espacio</t>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t>Títeres de dedo del Cuento Blancanieves y los siete enanitos</t>
+        </is>
+      </c>
+      <c r="O85" s="3" t="n">
+        <v>10300</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
           <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
-      </c>
-      <c r="C85" s="3" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Bolsito Amasando ideas Gato automovilista</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="n">
-        <v>12000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Bolsito Amasando ideas Pajaritos</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="n">
+          <t>Bolsito Amasando ideas Elefante</t>
+        </is>
+      </c>
+      <c r="O87" s="3" t="n">
         <v>12000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Dinosaurios</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="n">
-        <v>19500</v>
+          <t>Bolsito Amasando ideas Espacio</t>
+        </is>
+      </c>
+      <c r="O88" s="3" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Haditas</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="n">
-        <v>19500</v>
+          <t>Bolsito Amasando ideas Gato automovilista</t>
+        </is>
+      </c>
+      <c r="O89" s="3" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Piratas</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="n">
-        <v>19500</v>
+          <t>Bolsito Amasando ideas Pajaritos</t>
+        </is>
+      </c>
+      <c r="O90" s="3" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Ponis</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="n">
+          <t>Valija de Arte Mini Artista, Dinosaurios</t>
+        </is>
+      </c>
+      <c r="O91" s="3" t="n">
         <v>19500</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Sirenitas</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="n">
+          <t>Valija de Arte Mini Artista, Haditas</t>
+        </is>
+      </c>
+      <c r="O92" s="3" t="n">
         <v>19500</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Superhéroes</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="n">
+          <t>Valija de Arte Mini Artista, Piratas</t>
+        </is>
+      </c>
+      <c r="O93" s="3" t="n">
         <v>19500</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Astronautas</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="n">
-        <v>25850</v>
+          <t>Valija de Arte Mini Artista, Ponis</t>
+        </is>
+      </c>
+      <c r="O94" s="3" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Cocodrilo en Submarino</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="n">
-        <v>25850</v>
+          <t>Valija de Arte Mini Artista, Sirenitas</t>
+        </is>
+      </c>
+      <c r="O95" s="3" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Gato Automovilista</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="n">
-        <v>25850</v>
+          <t>Valija de Arte Mini Artista, Superhéroes</t>
+        </is>
+      </c>
+      <c r="O96" s="3" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Monstruos</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="n">
+          <t>Valija de Arte Mis Diseños. Astronautas</t>
+        </is>
+      </c>
+      <c r="O97" s="3" t="n">
         <v>25850</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Nena con Globos</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="n">
+          <t>Valija de Arte Mis Diseños. Cocodrilo en Submarino</t>
+        </is>
+      </c>
+      <c r="O98" s="3" t="n">
         <v>25850</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Nena en Hamaca</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="n">
+          <t>Valija de Arte Mis Diseños. Gato Automovilista</t>
+        </is>
+      </c>
+      <c r="O99" s="3" t="n">
         <v>25850</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Princesa</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="n">
+          <t>Valija de Arte Mis Diseños. Monstruos</t>
+        </is>
+      </c>
+      <c r="O100" s="3" t="n">
         <v>25850</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Robots</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="n">
+          <t>Valija de Arte Mis Diseños. Nena con Globos</t>
+        </is>
+      </c>
+      <c r="O101" s="3" t="n">
         <v>25850</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Unicornio</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
+          <t>Valija de Arte Mis Diseños. Nena en Hamaca</t>
+        </is>
+      </c>
+      <c r="O102" s="3" t="n">
+        <v>25850</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
-      <c r="C102" s="3" t="n">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Valija de Arte Mis Diseños. Princesa</t>
+        </is>
+      </c>
+      <c r="O103" s="3" t="n">
         <v>25850</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Bolsito Chef nena</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="n">
-        <v>11500</v>
+          <t>Valija de Arte Mis Diseños. Robots</t>
+        </is>
+      </c>
+      <c r="O104" s="3" t="n">
+        <v>25850</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Bolsito Chef varón</t>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
+          <t>Valija de Arte Mis Diseños. Unicornio</t>
+        </is>
+      </c>
+      <c r="O105" s="3" t="n">
+        <v>25850</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
           <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
-      </c>
-      <c r="C105" s="3" t="n">
-        <v>11500</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Bolsito Explorador Jirafas</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="n">
-        <v>11500</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Bolsito Explorador África</t>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="n">
+          <t>Bolsito Chef nena</t>
+        </is>
+      </c>
+      <c r="O107" s="3" t="n">
         <v>11500</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Bolsito Mini Peluquería</t>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="n">
+          <t>Bolsito Chef varón</t>
+        </is>
+      </c>
+      <c r="O108" s="3" t="n">
         <v>11500</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Set de esqueleto y órganos del cuerpo humano para Docentes y Educadores</t>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="n">
-        <v>16500</v>
+          <t>Bolsito Explorador Jirafas</t>
+        </is>
+      </c>
+      <c r="O109" s="3" t="n">
+        <v>11500</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Valija de Mini Chef nena</t>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="n">
-        <v>21000</v>
+          <t>Bolsito Explorador África</t>
+        </is>
+      </c>
+      <c r="O110" s="3" t="n">
+        <v>11500</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Valija de Mini Chef varón</t>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="n">
-        <v>21000</v>
+          <t>Bolsito Mini Peluquería</t>
+        </is>
+      </c>
+      <c r="O111" s="3" t="n">
+        <v>11500</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Valija de Mini Doctor</t>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="n">
-        <v>37500</v>
+          <t>Set de esqueleto y órganos del cuerpo humano para Docentes y Educadores</t>
+        </is>
+      </c>
+      <c r="O112" s="3" t="n">
+        <v>16500</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Valija de Mini Exploradores</t>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="n">
-        <v>24800</v>
+          <t>Valija de Mini Chef nena</t>
+        </is>
+      </c>
+      <c r="O113" s="3" t="n">
+        <v>21000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Valija de Mini Jardineros</t>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="n">
-        <v>23500</v>
+          <t>Valija de Mini Chef varón</t>
+        </is>
+      </c>
+      <c r="O114" s="3" t="n">
+        <v>21000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Valija de Mini Maestra</t>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="n">
-        <v>28600</v>
+          <t>Valija de Mini Doctor</t>
+        </is>
+      </c>
+      <c r="O115" s="3" t="n">
+        <v>37500</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Valija de Mini Maestro</t>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="n">
-        <v>28600</v>
+          <t>Valija de Mini Exploradores</t>
+        </is>
+      </c>
+      <c r="O116" s="3" t="n">
+        <v>24800</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Valija de Mini Spa</t>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="n">
-        <v>29800</v>
+          <t>Valija de Mini Jardineros</t>
+        </is>
+      </c>
+      <c r="O117" s="3" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Valija de Mini Veterinarios</t>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="n">
-        <v>26400</v>
+          <t>Valija de Mini Maestra</t>
+        </is>
+      </c>
+      <c r="O118" s="3" t="n">
+        <v>28600</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Valija de Tarde de Mate</t>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="n">
-        <v>19500</v>
+          <t>Valija de Mini Maestro</t>
+        </is>
+      </c>
+      <c r="O119" s="3" t="n">
+        <v>28600</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Valija de Tardes de Té</t>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
+          <t>Valija de Mini Spa</t>
+        </is>
+      </c>
+      <c r="O120" s="3" t="n">
+        <v>29800</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
           <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
       </c>
-      <c r="C120" s="3" t="n">
-        <v>25000</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Valija de Mini Veterinarios</t>
+        </is>
+      </c>
+      <c r="O121" s="3" t="n">
+        <v>26400</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Disfraz de Anna (Frozen)</t>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="n">
-        <v>24850</v>
+          <t>Valija de Tarde de Mate</t>
+        </is>
+      </c>
+      <c r="O122" s="3" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Disfraz de Bella</t>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
+          <t>Valija de Tardes de Té</t>
+        </is>
+      </c>
+      <c r="O123" s="3" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
           <t>DISFRACES PARA NENAS</t>
         </is>
-      </c>
-      <c r="C123" s="3" t="n">
-        <v>23970</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Disfraz de Blancanieves</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="n">
-        <v>24850</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Disfraz de Cenicienta</t>
+          <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="n">
-        <v>23970</v>
+          <t>Disfraz de Anna (Frozen)</t>
+        </is>
+      </c>
+      <c r="O125" s="3" t="n">
+        <v>24850</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Disfraz de Elsa (Frozen)</t>
+          <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="n">
-        <v>24850</v>
+          <t>Disfraz de Bella</t>
+        </is>
+      </c>
+      <c r="O126" s="3" t="n">
+        <v>23970</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Disfraz de Mira K-Pop Demon Hunters</t>
+          <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="n">
-        <v>38500</v>
+          <t>Disfraz de Blancanieves</t>
+        </is>
+      </c>
+      <c r="O127" s="3" t="n">
+        <v>24850</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Disfraz de Moana</t>
+          <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="n">
-        <v>24500</v>
+          <t>Disfraz de Cenicienta</t>
+        </is>
+      </c>
+      <c r="O128" s="3" t="n">
+        <v>23970</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Disfraz de Mujer Maravilla</t>
+          <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="n">
-        <v>19850</v>
+          <t>Disfraz de Elsa (Frozen)</t>
+        </is>
+      </c>
+      <c r="O129" s="3" t="n">
+        <v>24850</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Disfraz de Princesa Aurora,  La Bella Durmiente</t>
+          <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="n">
-        <v>23970</v>
+          <t>Disfraz de Mira K-Pop Demon Hunters</t>
+        </is>
+      </c>
+      <c r="O130" s="3" t="n">
+        <v>38500</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Disfraz de Rapunzel Encantada</t>
+          <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="n">
-        <v>33300</v>
+          <t>Disfraz de Moana</t>
+        </is>
+      </c>
+      <c r="O131" s="3" t="n">
+        <v>24500</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Disfraz de Rumi K-Pop Demon Hunters</t>
+          <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="n">
-        <v>28500</v>
+          <t>Disfraz de Mujer Maravilla</t>
+        </is>
+      </c>
+      <c r="O132" s="3" t="n">
+        <v>19850</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Disfraz de Rumi K-Pop Demon Hunters (Traje de colores con Chaqueta amarilla)</t>
+          <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="n">
-        <v>51800</v>
+          <t>Disfraz de Princesa Aurora,  La Bella Durmiente</t>
+        </is>
+      </c>
+      <c r="O133" s="3" t="n">
+        <v>23970</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Disfraz de Rumi K-Pop Demon Hunters, con Chaqueta y encanto dorado</t>
+          <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="n">
-        <v>53200</v>
+          <t>Disfraz de Rapunzel Encantada</t>
+        </is>
+      </c>
+      <c r="O134" s="3" t="n">
+        <v>33300</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Disfraz de Sirenita</t>
+          <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="n">
-        <v>22500</v>
+          <t>Disfraz de Rumi K-Pop Demon Hunters</t>
+        </is>
+      </c>
+      <c r="O135" s="3" t="n">
+        <v>28500</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Disfraz de Unicornio Mágico</t>
+          <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="n">
-        <v>27400</v>
+          <t>Disfraz de Rumi K-Pop Demon Hunters (Traje de colores con Chaqueta amarilla)</t>
+        </is>
+      </c>
+      <c r="O136" s="3" t="n">
+        <v>51800</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Disfraz de Zoey  K-Pop Demon Hunters</t>
+          <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="n">
-        <v>45000</v>
+          <t>Disfraz de Rumi K-Pop Demon Hunters, con Chaqueta y encanto dorado</t>
+        </is>
+      </c>
+      <c r="O137" s="3" t="n">
+        <v>53200</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Tutú de Bailarina Unicornio</t>
+          <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="n">
-        <v>23200</v>
+          <t>Disfraz de Sirenita</t>
+        </is>
+      </c>
+      <c r="O138" s="3" t="n">
+        <v>22500</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Tutú de bailarina</t>
+          <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
+          <t>Disfraz de Unicornio Mágico</t>
+        </is>
+      </c>
+      <c r="O139" s="3" t="n">
+        <v>27400</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
           <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
-      <c r="C139" s="3" t="n">
-        <v>19500</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>DISFRACES PARA NENES</t>
-        </is>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Disfraz de Zoey  K-Pop Demon Hunters</t>
+        </is>
+      </c>
+      <c r="O140" s="3" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Disfraz de Batman</t>
+          <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENES</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="n">
-        <v>23500</v>
+          <t>Tutú de Bailarina Unicornio</t>
+        </is>
+      </c>
+      <c r="O141" s="3" t="n">
+        <v>23200</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Disfraz de Bombero</t>
+          <t>DISFRACES PARA NENAS</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
+          <t>Tutú de bailarina</t>
+        </is>
+      </c>
+      <c r="O142" s="3" t="n">
+        <v>19500</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
           <t>DISFRACES PARA NENES</t>
         </is>
-      </c>
-      <c r="C142" s="3" t="n">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Disfraz de Capitán América</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>DISFRACES PARA NENES</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="n">
-        <v>23500</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Disfraz de Hombre Araña</t>
+          <t>DISFRACES PARA NENES</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENES</t>
-        </is>
-      </c>
-      <c r="C144" s="3" t="n">
-        <v>18000</v>
+          <t>Disfraz de Batman</t>
+        </is>
+      </c>
+      <c r="O144" s="3" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Disfraz de Pirata</t>
+          <t>DISFRACES PARA NENES</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENES</t>
-        </is>
-      </c>
-      <c r="C145" s="3" t="n">
-        <v>18000</v>
+          <t>Disfraz de Bombero</t>
+        </is>
+      </c>
+      <c r="O145" s="3" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Disfraz de Policía</t>
+          <t>DISFRACES PARA NENES</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>DISFRACES PARA NENES</t>
-        </is>
-      </c>
-      <c r="C146" s="3" t="n">
-        <v>15000</v>
+          <t>Disfraz de Capitán América</t>
+        </is>
+      </c>
+      <c r="O146" s="3" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Disfraz de Superman</t>
+          <t>DISFRACES PARA NENES</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
+          <t>Disfraz de Hombre Araña</t>
+        </is>
+      </c>
+      <c r="O147" s="3" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
           <t>DISFRACES PARA NENES</t>
         </is>
       </c>
-      <c r="C147" s="3" t="n">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>DISFRACES DE ANIMALITOS</t>
-        </is>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Disfraz de Pirata</t>
+        </is>
+      </c>
+      <c r="O148" s="3" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Disfraz de Araña</t>
+          <t>DISFRACES PARA NENES</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>DISFRACES DE ANIMALITOS</t>
-        </is>
-      </c>
-      <c r="C149" s="3" t="n">
-        <v>23500</v>
+          <t>Disfraz de Policía</t>
+        </is>
+      </c>
+      <c r="O149" s="3" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Disfraz de Cebra</t>
+          <t>DISFRACES PARA NENES</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
+          <t>Disfraz de Superman</t>
+        </is>
+      </c>
+      <c r="O150" s="3" t="n">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
           <t>DISFRACES DE ANIMALITOS</t>
         </is>
-      </c>
-      <c r="C150" s="3" t="n">
-        <v>23500</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Disfraz de Dinosaurio</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>DISFRACES DE ANIMALITOS</t>
-        </is>
-      </c>
-      <c r="C151" s="3" t="n">
-        <v>25200</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Disfraz de Tigre</t>
+          <t>DISFRACES DE ANIMALITOS</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
+          <t>Disfraz de Araña</t>
+        </is>
+      </c>
+      <c r="O152" s="3" t="n">
+        <v>23500</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
           <t>DISFRACES DE ANIMALITOS</t>
         </is>
       </c>
-      <c r="C152" s="3" t="n">
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Disfraz de Cebra</t>
+        </is>
+      </c>
+      <c r="O153" s="3" t="n">
         <v>23500</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Caramelera Calabaza</t>
+          <t>DISFRACES DE ANIMALITOS</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C154" s="3" t="n">
-        <v>9000</v>
+          <t>Disfraz de Dinosaurio</t>
+        </is>
+      </c>
+      <c r="O154" s="3" t="n">
+        <v>25200</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Disfraz de Araña</t>
+          <t>DISFRACES DE ANIMALITOS</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
+          <t>Disfraz de Tigre</t>
+        </is>
+      </c>
+      <c r="O155" s="3" t="n">
+        <v>23500</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
           <t>DISFRACES DE HALLOWEEN</t>
         </is>
-      </c>
-      <c r="C155" s="3" t="n">
-        <v>23500</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Disfraz de Brujita Fuxia</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C156" s="3" t="n">
-        <v>25500</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Naranja</t>
+          <t>DISFRACES DE HALLOWEEN</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C157" s="3" t="n">
-        <v>25500</v>
+          <t>Caramelera Calabaza</t>
+        </is>
+      </c>
+      <c r="O157" s="3" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Verde</t>
+          <t>DISFRACES DE HALLOWEEN</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C158" s="3" t="n">
-        <v>25500</v>
+          <t>Disfraz de Araña</t>
+        </is>
+      </c>
+      <c r="O158" s="3" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Violeta</t>
+          <t>DISFRACES DE HALLOWEEN</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C159" s="3" t="n">
+          <t>Disfraz de Brujita Fuxia</t>
+        </is>
+      </c>
+      <c r="O159" s="3" t="n">
         <v>25500</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Disfraz de Calabaza</t>
+          <t>DISFRACES DE HALLOWEEN</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C160" s="3" t="n">
-        <v>23500</v>
+          <t>Disfraz de Brujita Naranja</t>
+        </is>
+      </c>
+      <c r="O160" s="3" t="n">
+        <v>25500</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Disfraz de Esqueleto</t>
+          <t>DISFRACES DE HALLOWEEN</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C161" s="3" t="n">
-        <v>25000</v>
+          <t>Disfraz de Brujita Verde</t>
+        </is>
+      </c>
+      <c r="O161" s="3" t="n">
+        <v>25500</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Disfraz de Merlina</t>
+          <t>DISFRACES DE HALLOWEEN</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="C162" s="3" t="n">
-        <v>32000</v>
+          <t>Disfraz de Brujita Violeta</t>
+        </is>
+      </c>
+      <c r="O162" s="3" t="n">
+        <v>25500</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Disfraz de Vampira</t>
+          <t>DISFRACES DE HALLOWEEN</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
+          <t>Disfraz de Calabaza</t>
+        </is>
+      </c>
+      <c r="O163" s="3" t="n">
+        <v>23500</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
           <t>DISFRACES DE HALLOWEEN</t>
         </is>
       </c>
-      <c r="C163" s="3" t="n">
-        <v>25300</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Disfraz de Esqueleto</t>
+        </is>
+      </c>
+      <c r="O164" s="3" t="n">
+        <v>25000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Cesto para juguetes Cactus</t>
+          <t>DISFRACES DE HALLOWEEN</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="n">
-        <v>22900</v>
+          <t>Disfraz de Merlina</t>
+        </is>
+      </c>
+      <c r="O165" s="3" t="n">
+        <v>32000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Cesto para juguetes Cebra y Jirafa</t>
+          <t>DISFRACES DE HALLOWEEN</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
+          <t>Disfraz de Vampira</t>
+        </is>
+      </c>
+      <c r="O166" s="3" t="n">
+        <v>25300</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
           <t>JUGUETES PARA BEBÉS</t>
         </is>
-      </c>
-      <c r="C166" s="3" t="n">
-        <v>22900</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Cesto para juguetes Gatitos</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="n">
-        <v>22900</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Cesto para juguetes Indi</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C168" s="3" t="n">
+          <t>Cesto para juguetes Cactus</t>
+        </is>
+      </c>
+      <c r="O168" s="3" t="n">
         <v>22900</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Globo Pelota Animalitos</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C169" s="3" t="n">
-        <v>6800</v>
+          <t>Cesto para juguetes Cebra y Jirafa</t>
+        </is>
+      </c>
+      <c r="O169" s="3" t="n">
+        <v>22900</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Globo Pelota Dinosaurios</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="n">
-        <v>6800</v>
+          <t>Cesto para juguetes Gatitos</t>
+        </is>
+      </c>
+      <c r="O170" s="3" t="n">
+        <v>22900</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Globo Pelota Gatitos</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="n">
-        <v>6800</v>
+          <t>Cesto para juguetes Indi</t>
+        </is>
+      </c>
+      <c r="O171" s="3" t="n">
+        <v>22900</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Globo Pelota Haditas</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C172" s="3" t="n">
+          <t>Globo Pelota Animalitos</t>
+        </is>
+      </c>
+      <c r="O172" s="3" t="n">
         <v>6800</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Globo Pelota Monstruos</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C173" s="3" t="n">
+          <t>Globo Pelota Dinosaurios</t>
+        </is>
+      </c>
+      <c r="O173" s="3" t="n">
         <v>6800</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Globo Pelota Selva</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="n">
+          <t>Globo Pelota Gatitos</t>
+        </is>
+      </c>
+      <c r="O174" s="3" t="n">
         <v>6800</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Libro para bebé "Coral"</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C175" s="3" t="n">
-        <v>8400</v>
+          <t>Globo Pelota Haditas</t>
+        </is>
+      </c>
+      <c r="O175" s="3" t="n">
+        <v>6800</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Libro para bebé "Cosquillitas"</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C176" s="3" t="n">
-        <v>8400</v>
+          <t>Globo Pelota Monstruos</t>
+        </is>
+      </c>
+      <c r="O176" s="3" t="n">
+        <v>6800</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Libro para bebé "Mariposas"</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C177" s="3" t="n">
-        <v>8400</v>
+          <t>Globo Pelota Selva</t>
+        </is>
+      </c>
+      <c r="O177" s="3" t="n">
+        <v>6800</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Manta para bebé "Animalitos de la Selva"</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C178" s="3" t="n">
-        <v>15600</v>
+          <t>Libro para bebé "Coral"</t>
+        </is>
+      </c>
+      <c r="O178" s="3" t="n">
+        <v>8400</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Manta para bebé "La Ciudad"</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C179" s="3" t="n">
-        <v>15600</v>
+          <t>Libro para bebé "Cosquillitas"</t>
+        </is>
+      </c>
+      <c r="O179" s="3" t="n">
+        <v>8400</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Manta para bebé "Mininos"</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C180" s="3" t="n">
-        <v>15600</v>
+          <t>Libro para bebé "Mariposas"</t>
+        </is>
+      </c>
+      <c r="O180" s="3" t="n">
+        <v>8400</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Pelota de Trapo  Animalitos</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C181" s="3" t="n">
-        <v>15950</v>
+          <t>Manta para bebé "Animalitos de la Selva"</t>
+        </is>
+      </c>
+      <c r="O181" s="3" t="n">
+        <v>15600</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Pelota de Trapo  Dinosaurios</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C182" s="3" t="n">
-        <v>15950</v>
+          <t>Manta para bebé "La Ciudad"</t>
+        </is>
+      </c>
+      <c r="O182" s="3" t="n">
+        <v>15600</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Pelota de Trapo Gatitos</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C183" s="3" t="n">
-        <v>15950</v>
+          <t>Manta para bebé "Mininos"</t>
+        </is>
+      </c>
+      <c r="O183" s="3" t="n">
+        <v>15600</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Pelota de Trapo Selva</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C184" s="3" t="n">
+          <t>Pelota de Trapo  Animalitos</t>
+        </is>
+      </c>
+      <c r="O184" s="3" t="n">
         <v>15950</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Pulpitos Reversibles con dos emociones (alegre/ enojado)</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="C185" s="3" t="n">
-        <v>7500</v>
+          <t>Pelota de Trapo  Dinosaurios</t>
+        </is>
+      </c>
+      <c r="O185" s="3" t="n">
+        <v>15950</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Rayuela de tela para aprender los números jugando</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
+          <t>Pelota de Trapo Gatitos</t>
+        </is>
+      </c>
+      <c r="O186" s="3" t="n">
+        <v>15950</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
           <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
-      <c r="C186" s="3" t="n">
-        <v>24500</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
-        <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Pelota de Trapo Selva</t>
+        </is>
+      </c>
+      <c r="O187" s="3" t="n">
+        <v>15950</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Aurora</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C188" s="3" t="n">
-        <v>24350</v>
+          <t>Pulpitos Reversibles con dos emociones (alegre/ enojado)</t>
+        </is>
+      </c>
+      <c r="O188" s="3" t="n">
+        <v>7500</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Bella</t>
+          <t>JUGUETES PARA BEBÉS</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
+          <t>Rayuela de tela para aprender los números jugando</t>
+        </is>
+      </c>
+      <c r="O189" s="3" t="n">
+        <v>24500</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
           <t>MUÑECAS DE TRAPO</t>
         </is>
-      </c>
-      <c r="C189" s="3" t="n">
-        <v>24350</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Muñeca Piccolina Blancanieves</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C190" s="3" t="n">
-        <v>24350</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Cenicienta</t>
+          <t>MUÑECAS DE TRAPO</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C191" s="3" t="n">
+          <t>Muñeca Piccolina Aurora</t>
+        </is>
+      </c>
+      <c r="O191" s="3" t="n">
         <v>24350</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Coqueta</t>
+          <t>MUÑECAS DE TRAPO</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C192" s="3" t="n">
+          <t>Muñeca Piccolina Bella</t>
+        </is>
+      </c>
+      <c r="O192" s="3" t="n">
         <v>24350</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Deportiva</t>
+          <t>MUÑECAS DE TRAPO</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C193" s="3" t="n">
+          <t>Muñeca Piccolina Blancanieves</t>
+        </is>
+      </c>
+      <c r="O193" s="3" t="n">
         <v>24350</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Folk</t>
+          <t>MUÑECAS DE TRAPO</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C194" s="3" t="n">
+          <t>Muñeca Piccolina Cenicienta</t>
+        </is>
+      </c>
+      <c r="O194" s="3" t="n">
         <v>24350</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Jardinera</t>
+          <t>MUÑECAS DE TRAPO</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C195" s="3" t="n">
+          <t>Muñeca Piccolina Coqueta</t>
+        </is>
+      </c>
+      <c r="O195" s="3" t="n">
         <v>24350</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Rapunsel</t>
+          <t>MUÑECAS DE TRAPO</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C196" s="3" t="n">
+          <t>Muñeca Piccolina Deportiva</t>
+        </is>
+      </c>
+      <c r="O196" s="3" t="n">
         <v>24350</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Romántica</t>
+          <t>MUÑECAS DE TRAPO</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C197" s="3" t="n">
+          <t>Muñeca Piccolina Folk</t>
+        </is>
+      </c>
+      <c r="O197" s="3" t="n">
         <v>24350</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Sofía</t>
+          <t>MUÑECAS DE TRAPO</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C198" s="3" t="n">
+          <t>Muñeca Piccolina Jardinera</t>
+        </is>
+      </c>
+      <c r="O198" s="3" t="n">
         <v>24350</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina doctora</t>
+          <t>MUÑECAS DE TRAPO</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C199" s="3" t="n">
+          <t>Muñeca Piccolina Rapunsel</t>
+        </is>
+      </c>
+      <c r="O199" s="3" t="n">
         <v>24350</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Traje de doctora para muñecas</t>
+          <t>MUÑECAS DE TRAPO</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C200" s="3" t="n">
-        <v>8300</v>
+          <t>Muñeca Piccolina Romántica</t>
+        </is>
+      </c>
+      <c r="O200" s="3" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Traje de jardinera para muñecas</t>
+          <t>MUÑECAS DE TRAPO</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C201" s="3" t="n">
-        <v>8300</v>
+          <t>Muñeca Piccolina Sofía</t>
+        </is>
+      </c>
+      <c r="O201" s="3" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Traje deportivo para muñecas</t>
+          <t>MUÑECAS DE TRAPO</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C202" s="3" t="n">
-        <v>8300</v>
+          <t>Muñeca Piccolina doctora</t>
+        </is>
+      </c>
+      <c r="O202" s="3" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Vestido campesino para muñecas</t>
+          <t>MUÑECAS DE TRAPO</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C203" s="3" t="n">
+          <t>Traje de doctora para muñecas</t>
+        </is>
+      </c>
+      <c r="O203" s="3" t="n">
         <v>8300</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Vestido coqueta para muñecas</t>
+          <t>MUÑECAS DE TRAPO</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C204" s="3" t="n">
+          <t>Traje de jardinera para muñecas</t>
+        </is>
+      </c>
+      <c r="O204" s="3" t="n">
         <v>8300</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Vestido de Aurora para muñecas</t>
+          <t>MUÑECAS DE TRAPO</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C205" s="3" t="n">
+          <t>Traje deportivo para muñecas</t>
+        </is>
+      </c>
+      <c r="O205" s="3" t="n">
         <v>8300</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Vestido de Bella para muñecas</t>
+          <t>MUÑECAS DE TRAPO</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C206" s="3" t="n">
+          <t>Vestido campesino para muñecas</t>
+        </is>
+      </c>
+      <c r="O206" s="3" t="n">
         <v>8300</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Vestido de Blancanieves para muñecas</t>
+          <t>MUÑECAS DE TRAPO</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C207" s="3" t="n">
+          <t>Vestido coqueta para muñecas</t>
+        </is>
+      </c>
+      <c r="O207" s="3" t="n">
         <v>8300</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Vestido de Cenicienta para muñecas</t>
+          <t>MUÑECAS DE TRAPO</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C208" s="3" t="n">
+          <t>Vestido de Aurora para muñecas</t>
+        </is>
+      </c>
+      <c r="O208" s="3" t="n">
         <v>8300</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Vestido de Princesa Sofía para muñecas</t>
+          <t>MUÑECAS DE TRAPO</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C209" s="3" t="n">
+          <t>Vestido de Bella para muñecas</t>
+        </is>
+      </c>
+      <c r="O209" s="3" t="n">
         <v>8300</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Vestido de Rapunzel para muñecas</t>
+          <t>MUÑECAS DE TRAPO</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C210" s="3" t="n">
+          <t>Vestido de Blancanieves para muñecas</t>
+        </is>
+      </c>
+      <c r="O210" s="3" t="n">
         <v>8300</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Vestido de Cenicienta para muñecas</t>
+        </is>
+      </c>
+      <c r="O211" s="3" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Vestido de Princesa Sofía para muñecas</t>
+        </is>
+      </c>
+      <c r="O212" s="3" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Vestido de Rapunzel para muñecas</t>
+        </is>
+      </c>
+      <c r="O213" s="3" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
           <t>Vestido romántico para muñecas</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="C211" s="3" t="n">
+      <c r="O214" s="3" t="n">
         <v>8300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A83:O83"/>
-    <mergeCell ref="A148:O148"/>
-    <mergeCell ref="A25:O25"/>
-    <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A187:O187"/>
-    <mergeCell ref="A121:O121"/>
-    <mergeCell ref="A47:O47"/>
-    <mergeCell ref="A103:O103"/>
-    <mergeCell ref="A164:O164"/>
-    <mergeCell ref="A153:O153"/>
-    <mergeCell ref="A140:O140"/>
+    <mergeCell ref="A156:O156"/>
+    <mergeCell ref="A190:O190"/>
+    <mergeCell ref="A86:O86"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="A151:O151"/>
+    <mergeCell ref="A5:O5"/>
+    <mergeCell ref="A167:O167"/>
+    <mergeCell ref="A50:O50"/>
+    <mergeCell ref="A143:O143"/>
+    <mergeCell ref="A106:O106"/>
+    <mergeCell ref="A124:O124"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lista_precios_clientes.xlsx
+++ b/lista_precios_clientes.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +29,20 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="20"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="14"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,8 +57,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F9E4C8"/>
+        <bgColor rgb="00F9E4C8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F4A62A"/>
         <bgColor rgb="00F4A62A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2E2"/>
+        <bgColor rgb="00FFF2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -67,15 +86,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -441,11 +477,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:O214"/>
+  <dimension ref="A1:M216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -457,122 +493,101 @@
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LISTA MAYORISTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Lo Pequeño es Hermoso</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Actualizada automáticamente</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>Set con 1 títere</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>Set con 2 títeres</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Precio mayorista</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Set con 3 títeres</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Set con 4 títeres</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Set con 5 títeres</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Set con 6 títeres</t>
         </is>
       </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Set con 7 títeres</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>Set con 8 títeres</t>
         </is>
       </c>
-      <c r="K4" s="1" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>Set con 9 títeres</t>
         </is>
       </c>
-      <c r="L4" s="1" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Set con 10 títeres</t>
         </is>
       </c>
-      <c r="M4" s="1" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>Set con 11 títeres</t>
         </is>
       </c>
-      <c r="N4" s="1" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>Set con 12 títeres</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr">
-        <is>
-          <t>Precio mayorista</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>TÍTERES DE MANO</t>
         </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Blancanieves y los Siete Enanitos. Títeres de Mano y de Dedo.</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>29450</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TÍTERES DE MANO</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Caperucita Roja. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>20300</v>
       </c>
     </row>
     <row r="8">
@@ -583,11 +598,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cuento de Hadas. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>20300</v>
+          <t>Blancanieves y los Siete Enanitos. Títeres de Mano y de Dedo.</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>29450</v>
       </c>
     </row>
     <row r="9">
@@ -598,10 +613,10 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cuento de Príncipe Sapo y su Princesa. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="n">
+          <t>Caperucita Roja. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
         <v>20300</v>
       </c>
     </row>
@@ -613,10 +628,10 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>El Circo Mágico. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="n">
+          <t>Cuento de Hadas. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
         <v>20300</v>
       </c>
     </row>
@@ -628,11 +643,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>El Pesebre de Navideño. Títeres de Mano.</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>41200</v>
+          <t>Cuento de Príncipe Sapo y su Princesa. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>20300</v>
       </c>
     </row>
     <row r="12">
@@ -643,23 +658,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Heroínas de Cuentos Clásicos. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>15400</v>
-      </c>
-      <c r="F12" s="3" t="n">
+          <t>El Circo Mágico. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
         <v>20300</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>25200</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>30200</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>35100</v>
       </c>
     </row>
     <row r="13">
@@ -670,29 +673,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>La Familia Monte Espino. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>20300</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>25200</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>30200</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>35100</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>39960</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>44900</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>54750</v>
+          <t>El Pesebre de Navideño. Títeres de Mano.</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>41200</v>
       </c>
     </row>
     <row r="14">
@@ -703,35 +688,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>La Granja Arcoíris. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>11850</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>16500</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>19700</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>22860</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>26100</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>29300</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>33200</v>
-      </c>
-      <c r="M14" s="3" t="n">
-        <v>35700</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>38800</v>
+          <t>Heroínas de Cuentos Clásicos. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>15400</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>20300</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>25200</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>30200</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>35100</v>
       </c>
     </row>
     <row r="15">
@@ -742,14 +715,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>La Prehistoria: Dinosaurios y Cavernícolas. Títeres de mano.</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>11200</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>19960</v>
+          <t>La Familia Monte Espino. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>20300</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>25200</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>30200</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>35100</v>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>39960</v>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>44900</v>
+      </c>
+      <c r="K15" s="8" t="n">
+        <v>54750</v>
       </c>
     </row>
     <row r="16">
@@ -760,23 +748,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>La Selva Africana. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="n">
+          <t>La Granja Arcoíris. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="n">
         <v>11850</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="F16" s="8" t="n">
         <v>16500</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="G16" s="8" t="n">
         <v>19700</v>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="H16" s="8" t="n">
         <v>22860</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="I16" s="8" t="n">
         <v>26100</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>29300</v>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>33200</v>
+      </c>
+      <c r="L16" s="8" t="n">
+        <v>35700</v>
+      </c>
+      <c r="M16" s="8" t="n">
+        <v>38800</v>
       </c>
     </row>
     <row r="17">
@@ -787,11 +787,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>La Selva Misionera Argentina. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>19000</v>
+          <t>La Prehistoria: Dinosaurios y Cavernícolas. Títeres de mano.</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>11200</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>19960</v>
       </c>
     </row>
     <row r="18">
@@ -802,11 +805,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>La Sirenita. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="n">
-        <v>25200</v>
+          <t>La Selva Africana. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>11850</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>16500</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>19700</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>22860</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>26100</v>
       </c>
     </row>
     <row r="19">
@@ -817,11 +832,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Las Emociones. Títeres de Mano de Nena</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>30200</v>
+          <t>La Selva Misionera Argentina. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>19000</v>
       </c>
     </row>
     <row r="20">
@@ -832,11 +847,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Las Emociones. Títeres de Mano de Nene</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>30200</v>
+          <t>La Sirenita. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>25200</v>
       </c>
     </row>
     <row r="21">
@@ -847,11 +862,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Los 3 Chanchitos y el Lobo Feroz . Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="O21" s="3" t="n">
-        <v>11850</v>
+          <t>Las Emociones. Títeres de Mano de Nena</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>30200</v>
       </c>
     </row>
     <row r="22">
@@ -862,11 +877,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Los Esteros del Iberá. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>23200</v>
+          <t>Las Emociones. Títeres de Mano de Nene</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>30200</v>
       </c>
     </row>
     <row r="23">
@@ -877,11 +892,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Los Piratas Siete Mares. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="n">
-        <v>20300</v>
+          <t>Los 3 Chanchitos y el Lobo Feroz . Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>11850</v>
       </c>
     </row>
     <row r="24">
@@ -892,14 +907,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mis amigos los animalitos domésticos . Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>16500</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>26350</v>
+          <t>Los Esteros del Iberá. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>23200</v>
       </c>
     </row>
     <row r="25">
@@ -910,11 +922,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Navidad. Títeres de Mano.</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="n">
-        <v>11200</v>
+          <t>Los Piratas Siete Mares. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>20300</v>
       </c>
     </row>
     <row r="26">
@@ -925,11 +937,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Superhéroes. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="n">
-        <v>20300</v>
+          <t>Mis amigos los animalitos domésticos . Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>16500</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>26350</v>
       </c>
     </row>
     <row r="27">
@@ -940,72 +955,72 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Títeres Patrios. Títeres de Mano</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>11850</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>16500</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>19700</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>22860</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>26100</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>29300</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>33200</v>
-      </c>
-      <c r="M27" s="3" t="n">
-        <v>35700</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>38800</v>
+          <t>Navidad. Títeres de Mano.</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>11200</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Superhéroes. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>20300</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>TÍTERES DE MANO</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Títeres Patrios. Títeres de Mano</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>11850</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>16500</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>19700</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>22860</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>26100</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>29300</v>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>33200</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>35700</v>
+      </c>
+      <c r="M29" s="8" t="n">
+        <v>38800</v>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
           <t>TEATROS CON TÍTERES</t>
         </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Teatro "El Circo Mágico" con Títeres de Artistas</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="n">
-        <v>36800</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TEATROS CON TÍTERES</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Teatro Barco con Títeres de Los Piratas de los Siete Mares.</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="n">
-        <v>36800</v>
       </c>
     </row>
     <row r="31">
@@ -1016,11 +1031,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Teatro Bosque con Títeres del cuento "Los tres Chanchitos y el Lobo Feroz"</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="n">
-        <v>29800</v>
+          <t>Teatro "El Circo Mágico" con Títeres de Artistas</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>36800</v>
       </c>
     </row>
     <row r="32">
@@ -1031,10 +1046,10 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Teatro Castillo con Títeres de Cuento de Hadas</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="n">
+          <t>Teatro Barco con Títeres de Los Piratas de los Siete Mares.</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n">
         <v>36800</v>
       </c>
     </row>
@@ -1046,20 +1061,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Teatro Castillo con Títeres de Heroínas de Cuentos Clásicos.</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>36800</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>41700</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>46600</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>48100</v>
+          <t>Teatro Bosque con Títeres del cuento "Los tres Chanchitos y el Lobo Feroz"</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>29800</v>
       </c>
     </row>
     <row r="34">
@@ -1070,10 +1076,10 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Teatro Castillo con Títeres del Cuento "Príncipe Sapo y su Princesa"</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="n">
+          <t>Teatro Castillo con Títeres de Cuento de Hadas</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n">
         <v>36800</v>
       </c>
     </row>
@@ -1085,19 +1091,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con Títeres de La Familia Monte Espino</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="n">
+          <t>Teatro Castillo con Títeres de Heroínas de Cuentos Clásicos.</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="n">
         <v>36800</v>
       </c>
-      <c r="G35" s="3" t="n">
+      <c r="F35" s="8" t="n">
         <v>41700</v>
       </c>
-      <c r="H35" s="3" t="n">
+      <c r="G35" s="8" t="n">
         <v>46600</v>
       </c>
-      <c r="I35" s="3" t="n">
+      <c r="H35" s="8" t="n">
         <v>48100</v>
       </c>
     </row>
@@ -1109,17 +1115,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con Títeres de Nene y sus Emociones</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="n">
+          <t>Teatro Castillo con Títeres del Cuento "Príncipe Sapo y su Princesa"</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="n">
         <v>36800</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>41700</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>46600</v>
       </c>
     </row>
     <row r="37">
@@ -1130,17 +1130,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con Títeres de nena y sus Emociones</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="n">
+          <t>Teatro Ciudad con Títeres de La Familia Monte Espino</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="n">
         <v>36800</v>
       </c>
-      <c r="G37" s="3" t="n">
+      <c r="F37" s="8" t="n">
         <v>41700</v>
       </c>
-      <c r="H37" s="3" t="n">
+      <c r="G37" s="8" t="n">
         <v>46600</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>48100</v>
       </c>
     </row>
     <row r="38">
@@ -1151,16 +1154,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Teatro Ciudad con títeres de niños animalitos domésticos</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="n">
+          <t>Teatro Ciudad con Títeres de Nene y sus Emociones</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="n">
         <v>36800</v>
       </c>
-      <c r="G38" s="3" t="n">
+      <c r="F38" s="8" t="n">
         <v>41700</v>
       </c>
-      <c r="H38" s="3" t="n">
+      <c r="G38" s="8" t="n">
         <v>46600</v>
       </c>
     </row>
@@ -1172,11 +1175,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Teatro Fondo del mar con Títeres de "La Sirenita"</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>38200</v>
+          <t>Teatro Ciudad con Títeres de nena y sus Emociones</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>36800</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>41700</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>46600</v>
       </c>
     </row>
     <row r="40">
@@ -1187,35 +1196,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Teatro Granja con Títeres de La Granja</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>29800</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>32980</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>36200</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>39400</v>
-      </c>
-      <c r="J40" s="3" t="n">
+          <t>Teatro Ciudad con títeres de niños animalitos domésticos</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>36800</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>41700</v>
+      </c>
+      <c r="G40" s="8" t="n">
         <v>46600</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>45800</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>48950</v>
-      </c>
-      <c r="M40" s="3" t="n">
-        <v>52100</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>55300</v>
       </c>
     </row>
     <row r="41">
@@ -1226,14 +1217,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Teatro Prehistoria con Títeres de Dinosaurios y Cavernícolas</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>28900</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>36500</v>
+          <t>Teatro Fondo del mar con Títeres de "La Sirenita"</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>38200</v>
       </c>
     </row>
     <row r="42">
@@ -1244,11 +1232,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Teatro Selva Misionera Argentina con Títeres de la Selva Misionera</t>
-        </is>
-      </c>
-      <c r="O42" s="3" t="n">
+          <t>Teatro Granja con Títeres de La Granja</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>29800</v>
+      </c>
+      <c r="F42" s="8" t="n">
         <v>32980</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>36200</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>39400</v>
+      </c>
+      <c r="I42" s="8" t="n">
+        <v>46600</v>
+      </c>
+      <c r="J42" s="8" t="n">
+        <v>45800</v>
+      </c>
+      <c r="K42" s="8" t="n">
+        <v>48950</v>
+      </c>
+      <c r="L42" s="8" t="n">
+        <v>52100</v>
+      </c>
+      <c r="M42" s="8" t="n">
+        <v>55300</v>
       </c>
     </row>
     <row r="43">
@@ -1259,23 +1271,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Teatro Selva con Títeres de la Selva Africana</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>29800</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>32980</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>36200</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>39400</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>46600</v>
+          <t>Teatro Prehistoria con Títeres de Dinosaurios y Cavernícolas</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>28900</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>36500</v>
       </c>
     </row>
     <row r="44">
@@ -1286,11 +1289,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Teatro bosque con Títeres de Caperucita Roja</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="n">
-        <v>36800</v>
+          <t>Teatro Selva Misionera Argentina con Títeres de la Selva Misionera</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>32980</v>
       </c>
     </row>
     <row r="45">
@@ -1301,11 +1304,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Teatro bosque con títeres de Blancanieves y los Siete Enanitos</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="n">
-        <v>34990</v>
+          <t>Teatro Selva con Títeres de la Selva Africana</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>29800</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>32980</v>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>36200</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>39400</v>
+      </c>
+      <c r="I45" s="8" t="n">
+        <v>46600</v>
       </c>
     </row>
     <row r="46">
@@ -1316,10 +1331,10 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Teatro ciudad con títeres de Superhéroes.</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="n">
+          <t>Teatro bosque con Títeres de Caperucita Roja</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="n">
         <v>36800</v>
       </c>
     </row>
@@ -1331,11 +1346,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Teatro de Títeres Didáctico Clásico para Escuelas y Jardines de Infantes</t>
-        </is>
-      </c>
-      <c r="O47" s="3" t="n">
-        <v>57800</v>
+          <t>Teatro bosque con títeres de Blancanieves y los Siete Enanitos</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>34990</v>
       </c>
     </row>
     <row r="48">
@@ -1346,35 +1361,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Teatro de la Época Colonial con Títeres Patrios</t>
-        </is>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>29800</v>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>32980</v>
-      </c>
-      <c r="H48" s="3" t="n">
-        <v>36200</v>
-      </c>
-      <c r="I48" s="3" t="n">
-        <v>39400</v>
-      </c>
-      <c r="J48" s="3" t="n">
-        <v>46600</v>
-      </c>
-      <c r="K48" s="3" t="n">
-        <v>45800</v>
-      </c>
-      <c r="L48" s="3" t="n">
-        <v>48950</v>
-      </c>
-      <c r="M48" s="3" t="n">
-        <v>52100</v>
-      </c>
-      <c r="N48" s="3" t="n">
-        <v>55300</v>
+          <t>Teatro ciudad con títeres de Superhéroes.</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>36800</v>
       </c>
     </row>
     <row r="49">
@@ -1385,48 +1376,72 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Teatro de los Esteros del Iberá Títeres de animales de los Esteros del Iberá</t>
-        </is>
-      </c>
-      <c r="O49" s="3" t="n">
+          <t>Teatro de Títeres Didáctico Clásico para Escuelas y Jardines de Infantes</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>57800</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Teatro de la Época Colonial con Títeres Patrios</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>29800</v>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>32980</v>
+      </c>
+      <c r="G50" s="8" t="n">
         <v>36200</v>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
+      <c r="H50" s="8" t="n">
+        <v>39400</v>
+      </c>
+      <c r="I50" s="8" t="n">
+        <v>46600</v>
+      </c>
+      <c r="J50" s="8" t="n">
+        <v>45800</v>
+      </c>
+      <c r="K50" s="8" t="n">
+        <v>48950</v>
+      </c>
+      <c r="L50" s="8" t="n">
+        <v>52100</v>
+      </c>
+      <c r="M50" s="8" t="n">
+        <v>55300</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>TEATROS CON TÍTERES</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Teatro de los Esteros del Iberá Títeres de animales de los Esteros del Iberá</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>36200</v>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
           <t>MINITEATROS Y TÍTERES DE DEDO</t>
         </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Mini teatro Barco Pirata con Títeres de dedo de Piratas</t>
-        </is>
-      </c>
-      <c r="O51" s="3" t="n">
-        <v>16300</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>MINITEATROS Y TÍTERES DE DEDO</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Mini teatro Bosque con Títeres de dedo del Cuento Blancanieves y los Siete Enanitos</t>
-        </is>
-      </c>
-      <c r="O52" s="3" t="n">
-        <v>18800</v>
       </c>
     </row>
     <row r="53">
@@ -1437,10 +1452,10 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mini teatro Bosque con Títeres de dedo del Cuento de Caperucita Roja</t>
-        </is>
-      </c>
-      <c r="O53" s="3" t="n">
+          <t>Mini teatro Barco Pirata con Títeres de dedo de Piratas</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="n">
         <v>16300</v>
       </c>
     </row>
@@ -1452,11 +1467,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Mini teatro Bosque con Títeres de dedo del cuento Los Tres Chanchitos y el Lobo</t>
-        </is>
-      </c>
-      <c r="O54" s="3" t="n">
-        <v>16300</v>
+          <t>Mini teatro Bosque con Títeres de dedo del Cuento Blancanieves y los Siete Enanitos</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>18800</v>
       </c>
     </row>
     <row r="55">
@@ -1467,11 +1482,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mini teatro Castillo con Títeres de dedo de Cuento Príncipe Encantado</t>
-        </is>
-      </c>
-      <c r="O55" s="3" t="n">
-        <v>18000</v>
+          <t>Mini teatro Bosque con Títeres de dedo del Cuento de Caperucita Roja</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>16300</v>
       </c>
     </row>
     <row r="56">
@@ -1482,11 +1497,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mini teatro Castillo con Títeres de dedo de Cuento de Hadas</t>
-        </is>
-      </c>
-      <c r="O56" s="3" t="n">
-        <v>18800</v>
+          <t>Mini teatro Bosque con Títeres de dedo del cuento Los Tres Chanchitos y el Lobo</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>16300</v>
       </c>
     </row>
     <row r="57">
@@ -1497,20 +1512,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mini teatro Castillo con Títeres de dedo de Heroínas de Cuento</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>18800</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>21250</v>
-      </c>
-      <c r="H57" s="3" t="n">
-        <v>23670</v>
-      </c>
-      <c r="I57" s="3" t="n">
-        <v>26100</v>
+          <t>Mini teatro Castillo con Títeres de dedo de Cuento Príncipe Encantado</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="58">
@@ -1521,10 +1527,10 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mini teatro Circo con  Títeres de dedo de Artistas</t>
-        </is>
-      </c>
-      <c r="O58" s="3" t="n">
+          <t>Mini teatro Castillo con Títeres de dedo de Cuento de Hadas</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="n">
         <v>18800</v>
       </c>
     </row>
@@ -1536,20 +1542,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mini teatro Ciudad con Títeres de dedo de  Animalitos Domésticos</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="n">
-        <v>18150</v>
-      </c>
-      <c r="H59" s="3" t="n">
-        <v>19920</v>
-      </c>
-      <c r="I59" s="3" t="n">
-        <v>21800</v>
-      </c>
-      <c r="J59" s="3" t="n">
-        <v>23550</v>
+          <t>Mini teatro Castillo con Títeres de dedo de Heroínas de Cuento</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>18800</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>21250</v>
+      </c>
+      <c r="G59" s="8" t="n">
+        <v>23670</v>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>26100</v>
       </c>
     </row>
     <row r="60">
@@ -1560,20 +1566,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mini teatro Ciudad con Títeres de dedo de La Familia</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>16300</v>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>18150</v>
-      </c>
-      <c r="H60" s="3" t="n">
-        <v>19920</v>
-      </c>
-      <c r="I60" s="3" t="n">
-        <v>21800</v>
+          <t>Mini teatro Circo con  Títeres de dedo de Artistas</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>18800</v>
       </c>
     </row>
     <row r="61">
@@ -1584,11 +1581,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mini teatro Ciudad con Títeres de dedo de Superhéroes</t>
-        </is>
-      </c>
-      <c r="O61" s="3" t="n">
-        <v>18800</v>
+          <t>Mini teatro Ciudad con Títeres de dedo de  Animalitos Domésticos</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>18150</v>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>19920</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>21800</v>
+      </c>
+      <c r="I61" s="8" t="n">
+        <v>23550</v>
       </c>
     </row>
     <row r="62">
@@ -1599,11 +1605,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mini teatro Fondo del Mar con Títeres de dedo de La Sirenita</t>
-        </is>
-      </c>
-      <c r="O62" s="3" t="n">
-        <v>19980</v>
+          <t>Mini teatro Ciudad con Títeres de dedo de La Familia</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>16300</v>
+      </c>
+      <c r="F62" s="8" t="n">
+        <v>18150</v>
+      </c>
+      <c r="G62" s="8" t="n">
+        <v>19920</v>
+      </c>
+      <c r="H62" s="8" t="n">
+        <v>21800</v>
       </c>
     </row>
     <row r="63">
@@ -1614,17 +1629,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Mini teatro Prehistoria con Títeres de dedo de Dinosaurios y Cavernícolas</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>14500</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>16200</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>19360</v>
+          <t>Mini teatro Ciudad con Títeres de dedo de Superhéroes</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="n">
+        <v>18800</v>
       </c>
     </row>
     <row r="64">
@@ -1635,23 +1644,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mini teatro Selva con Títeres de dedo de la Selva Africana</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>16300</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>18150</v>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>19920</v>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>21800</v>
-      </c>
-      <c r="J64" s="3" t="n">
-        <v>23550</v>
+          <t>Mini teatro Fondo del Mar con Títeres de dedo de La Sirenita</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>19980</v>
       </c>
     </row>
     <row r="65">
@@ -1662,11 +1659,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mini teatro de los Esteros del iberá con Títeres de dedo de animalitos de Los Esteros del Iberá</t>
-        </is>
-      </c>
-      <c r="O65" s="3" t="n">
-        <v>19950</v>
+          <t>Mini teatro Prehistoria con Títeres de dedo de Dinosaurios y Cavernícolas</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="n">
+        <v>14500</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>16200</v>
+      </c>
+      <c r="F65" s="8" t="n">
+        <v>19360</v>
       </c>
     </row>
     <row r="66">
@@ -1677,29 +1680,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mini teatro granja con títeres de dedo de La Granja Arcoiris</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="n">
+          <t>Mini teatro Selva con Títeres de dedo de la Selva Africana</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="n">
         <v>16300</v>
       </c>
-      <c r="G66" s="3" t="n">
+      <c r="F66" s="8" t="n">
         <v>18150</v>
       </c>
-      <c r="H66" s="3" t="n">
+      <c r="G66" s="8" t="n">
         <v>19920</v>
       </c>
-      <c r="I66" s="3" t="n">
+      <c r="H66" s="8" t="n">
         <v>21800</v>
       </c>
-      <c r="J66" s="3" t="n">
+      <c r="I66" s="8" t="n">
         <v>23550</v>
-      </c>
-      <c r="K66" s="3" t="n">
-        <v>25350</v>
-      </c>
-      <c r="L66" s="3" t="n">
-        <v>27200</v>
       </c>
     </row>
     <row r="67">
@@ -1710,11 +1707,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Miniteatro de Selva Misionera Argentina con Títeres de dedo de la Selva Misionera Argentina</t>
-        </is>
-      </c>
-      <c r="O67" s="3" t="n">
-        <v>18200</v>
+          <t>Mini teatro de los Esteros del iberá con Títeres de dedo de animalitos de Los Esteros del Iberá</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>19950</v>
       </c>
     </row>
     <row r="68">
@@ -1725,11 +1722,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Títeres de dedo Pack x 10 unidades de animalitos</t>
-        </is>
-      </c>
-      <c r="O68" s="3" t="n">
-        <v>18000</v>
+          <t>Mini teatro granja con títeres de dedo de La Granja Arcoiris</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>16300</v>
+      </c>
+      <c r="F68" s="8" t="n">
+        <v>18150</v>
+      </c>
+      <c r="G68" s="8" t="n">
+        <v>19920</v>
+      </c>
+      <c r="H68" s="8" t="n">
+        <v>21800</v>
+      </c>
+      <c r="I68" s="8" t="n">
+        <v>23550</v>
+      </c>
+      <c r="J68" s="8" t="n">
+        <v>25350</v>
+      </c>
+      <c r="K68" s="8" t="n">
+        <v>27200</v>
       </c>
     </row>
     <row r="69">
@@ -1740,20 +1755,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Animalitos domésticos</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>7800</v>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>9600</v>
-      </c>
-      <c r="H69" s="3" t="n">
-        <v>11400</v>
-      </c>
-      <c r="I69" s="3" t="n">
-        <v>13200</v>
+          <t>Miniteatro de Selva Misionera Argentina con Títeres de dedo de la Selva Misionera Argentina</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>18200</v>
       </c>
     </row>
     <row r="70">
@@ -1764,11 +1770,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Caperucita roja</t>
-        </is>
-      </c>
-      <c r="O70" s="3" t="n">
-        <v>7800</v>
+          <t>Títeres de dedo Pack x 10 unidades de animalitos</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="71">
@@ -1779,11 +1785,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Cuento Príncipe Encantado</t>
-        </is>
-      </c>
-      <c r="O71" s="3" t="n">
-        <v>10300</v>
+          <t>Títeres de dedo de Animalitos domésticos</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>7800</v>
+      </c>
+      <c r="F71" s="8" t="n">
+        <v>9600</v>
+      </c>
+      <c r="G71" s="8" t="n">
+        <v>11400</v>
+      </c>
+      <c r="H71" s="8" t="n">
+        <v>13200</v>
       </c>
     </row>
     <row r="72">
@@ -1794,11 +1809,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Cuento de Hadas</t>
-        </is>
-      </c>
-      <c r="O72" s="3" t="n">
-        <v>10300</v>
+          <t>Títeres de dedo de Caperucita roja</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="n">
+        <v>7800</v>
       </c>
     </row>
     <row r="73">
@@ -1809,10 +1824,10 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Títeres de dedo de El Circo Mágico</t>
-        </is>
-      </c>
-      <c r="O73" s="3" t="n">
+          <t>Títeres de dedo de Cuento Príncipe Encantado</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="n">
         <v>10300</v>
       </c>
     </row>
@@ -1824,17 +1839,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Heroínas de cuento</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="n">
+          <t>Títeres de dedo de Cuento de Hadas</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="n">
         <v>10300</v>
-      </c>
-      <c r="G74" s="3" t="n">
-        <v>12700</v>
-      </c>
-      <c r="I74" s="3" t="n">
-        <v>17600</v>
       </c>
     </row>
     <row r="75">
@@ -1845,20 +1854,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Títeres de dedo de La Familia Monte Espino</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>7800</v>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>9600</v>
-      </c>
-      <c r="H75" s="3" t="n">
-        <v>11400</v>
-      </c>
-      <c r="I75" s="3" t="n">
-        <v>13200</v>
+          <t>Títeres de dedo de El Circo Mágico</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>10300</v>
       </c>
     </row>
     <row r="76">
@@ -1869,11 +1869,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Títeres de dedo de La Prehistoria</t>
-        </is>
-      </c>
-      <c r="O76" s="3" t="n">
-        <v>10825</v>
+          <t>Títeres de dedo de Heroínas de cuento</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>10300</v>
+      </c>
+      <c r="F76" s="8" t="n">
+        <v>12700</v>
+      </c>
+      <c r="H76" s="8" t="n">
+        <v>17600</v>
       </c>
     </row>
     <row r="77">
@@ -1884,11 +1890,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Títeres de dedo de La Sirenita</t>
-        </is>
-      </c>
-      <c r="O77" s="3" t="n">
-        <v>11450</v>
+          <t>Títeres de dedo de La Familia Monte Espino</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>7800</v>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>9600</v>
+      </c>
+      <c r="G77" s="8" t="n">
+        <v>11400</v>
+      </c>
+      <c r="H77" s="8" t="n">
+        <v>13200</v>
       </c>
     </row>
     <row r="78">
@@ -1899,20 +1914,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Los Esteros del Iberá</t>
-        </is>
-      </c>
-      <c r="F78" s="3" t="n">
-        <v>7800</v>
-      </c>
-      <c r="G78" s="3" t="n">
-        <v>9600</v>
-      </c>
-      <c r="H78" s="3" t="n">
-        <v>11400</v>
-      </c>
-      <c r="I78" s="3" t="n">
-        <v>13200</v>
+          <t>Títeres de dedo de La Prehistoria</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>10825</v>
       </c>
     </row>
     <row r="79">
@@ -1923,11 +1929,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Los Piratas Siete Mares</t>
-        </is>
-      </c>
-      <c r="O79" s="3" t="n">
-        <v>7800</v>
+          <t>Títeres de dedo de La Sirenita</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="n">
+        <v>11450</v>
       </c>
     </row>
     <row r="80">
@@ -1938,11 +1944,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Los Tres Chanchitos y el lobo</t>
-        </is>
-      </c>
-      <c r="O80" s="3" t="n">
+          <t>Títeres de dedo de Los Esteros del Iberá</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="n">
         <v>7800</v>
+      </c>
+      <c r="F80" s="8" t="n">
+        <v>9600</v>
+      </c>
+      <c r="G80" s="8" t="n">
+        <v>11400</v>
+      </c>
+      <c r="H80" s="8" t="n">
+        <v>13200</v>
       </c>
     </row>
     <row r="81">
@@ -1953,23 +1968,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Selva Africana</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="n">
+          <t>Títeres de dedo de Los Piratas Siete Mares</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="n">
         <v>7800</v>
-      </c>
-      <c r="G81" s="3" t="n">
-        <v>9600</v>
-      </c>
-      <c r="H81" s="3" t="n">
-        <v>11400</v>
-      </c>
-      <c r="I81" s="3" t="n">
-        <v>13200</v>
-      </c>
-      <c r="J81" s="3" t="n">
-        <v>15100</v>
       </c>
     </row>
     <row r="82">
@@ -1980,14 +1983,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Selva Misionera</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="n">
+          <t>Títeres de dedo de Los Tres Chanchitos y el lobo</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="n">
         <v>7800</v>
-      </c>
-      <c r="G82" s="3" t="n">
-        <v>9600</v>
       </c>
     </row>
     <row r="83">
@@ -1998,11 +1998,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Títeres de dedo de Superhéroes</t>
-        </is>
-      </c>
-      <c r="O83" s="3" t="n">
-        <v>10300</v>
+          <t>Títeres de dedo de Selva Africana</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>7800</v>
+      </c>
+      <c r="F83" s="8" t="n">
+        <v>9600</v>
+      </c>
+      <c r="G83" s="8" t="n">
+        <v>11400</v>
+      </c>
+      <c r="H83" s="8" t="n">
+        <v>13200</v>
+      </c>
+      <c r="I83" s="8" t="n">
+        <v>15100</v>
       </c>
     </row>
     <row r="84">
@@ -2013,23 +2025,14 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Títeres de dedo de granja</t>
-        </is>
-      </c>
-      <c r="F84" s="3" t="n">
+          <t>Títeres de dedo de Selva Misionera</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="n">
         <v>7800</v>
       </c>
-      <c r="G84" s="3" t="n">
+      <c r="F84" s="8" t="n">
         <v>9600</v>
-      </c>
-      <c r="H84" s="3" t="n">
-        <v>11400</v>
-      </c>
-      <c r="I84" s="3" t="n">
-        <v>13200</v>
-      </c>
-      <c r="J84" s="3" t="n">
-        <v>15100</v>
       </c>
     </row>
     <row r="85">
@@ -2040,48 +2043,60 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Títeres de dedo del Cuento Blancanieves y los siete enanitos</t>
-        </is>
-      </c>
-      <c r="O85" s="3" t="n">
+          <t>Títeres de dedo de Superhéroes</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="n">
         <v>10300</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Títeres de dedo de granja</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>7800</v>
+      </c>
+      <c r="F86" s="8" t="n">
+        <v>9600</v>
+      </c>
+      <c r="G86" s="8" t="n">
+        <v>11400</v>
+      </c>
+      <c r="H86" s="8" t="n">
+        <v>13200</v>
+      </c>
+      <c r="I86" s="8" t="n">
+        <v>15100</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>MINITEATROS Y TÍTERES DE DEDO</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Títeres de dedo del Cuento Blancanieves y los siete enanitos</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="n">
+        <v>10300</v>
+      </c>
+    </row>
+    <row r="88" ht="28" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
           <t>VALIJAS DIDÁCTICAS DE ARTE</t>
         </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Bolsito Amasando ideas Elefante</t>
-        </is>
-      </c>
-      <c r="O87" s="3" t="n">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Bolsito Amasando ideas Espacio</t>
-        </is>
-      </c>
-      <c r="O88" s="3" t="n">
-        <v>12000</v>
       </c>
     </row>
     <row r="89">
@@ -2092,10 +2107,10 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Bolsito Amasando ideas Gato automovilista</t>
-        </is>
-      </c>
-      <c r="O89" s="3" t="n">
+          <t>Bolsito Amasando ideas Elefante</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -2107,10 +2122,10 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Bolsito Amasando ideas Pajaritos</t>
-        </is>
-      </c>
-      <c r="O90" s="3" t="n">
+          <t>Bolsito Amasando ideas Espacio</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -2122,11 +2137,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Dinosaurios</t>
-        </is>
-      </c>
-      <c r="O91" s="3" t="n">
-        <v>19500</v>
+          <t>Bolsito Amasando ideas Gato automovilista</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="92">
@@ -2137,11 +2152,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Haditas</t>
-        </is>
-      </c>
-      <c r="O92" s="3" t="n">
-        <v>19500</v>
+          <t>Bolsito Amasando ideas Pajaritos</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="n">
+        <v>12000</v>
       </c>
     </row>
     <row r="93">
@@ -2152,10 +2167,10 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Piratas</t>
-        </is>
-      </c>
-      <c r="O93" s="3" t="n">
+          <t>Valija de Arte Mini Artista, Dinosaurios</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="n">
         <v>19500</v>
       </c>
     </row>
@@ -2167,10 +2182,10 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Ponis</t>
-        </is>
-      </c>
-      <c r="O94" s="3" t="n">
+          <t>Valija de Arte Mini Artista, Haditas</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="n">
         <v>19500</v>
       </c>
     </row>
@@ -2182,10 +2197,10 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Sirenitas</t>
-        </is>
-      </c>
-      <c r="O95" s="3" t="n">
+          <t>Valija de Arte Mini Artista, Piratas</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="n">
         <v>19500</v>
       </c>
     </row>
@@ -2197,10 +2212,10 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Valija de Arte Mini Artista, Superhéroes</t>
-        </is>
-      </c>
-      <c r="O96" s="3" t="n">
+          <t>Valija de Arte Mini Artista, Ponis</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="n">
         <v>19500</v>
       </c>
     </row>
@@ -2212,11 +2227,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Astronautas</t>
-        </is>
-      </c>
-      <c r="O97" s="3" t="n">
-        <v>25850</v>
+          <t>Valija de Arte Mini Artista, Sirenitas</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="98">
@@ -2227,11 +2242,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Cocodrilo en Submarino</t>
-        </is>
-      </c>
-      <c r="O98" s="3" t="n">
-        <v>25850</v>
+          <t>Valija de Arte Mini Artista, Superhéroes</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="99">
@@ -2242,10 +2257,10 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Gato Automovilista</t>
-        </is>
-      </c>
-      <c r="O99" s="3" t="n">
+          <t>Valija de Arte Mis Diseños. Astronautas</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="n">
         <v>25850</v>
       </c>
     </row>
@@ -2257,10 +2272,10 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Monstruos</t>
-        </is>
-      </c>
-      <c r="O100" s="3" t="n">
+          <t>Valija de Arte Mis Diseños. Cocodrilo en Submarino</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="n">
         <v>25850</v>
       </c>
     </row>
@@ -2272,10 +2287,10 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Nena con Globos</t>
-        </is>
-      </c>
-      <c r="O101" s="3" t="n">
+          <t>Valija de Arte Mis Diseños. Gato Automovilista</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="n">
         <v>25850</v>
       </c>
     </row>
@@ -2287,10 +2302,10 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Nena en Hamaca</t>
-        </is>
-      </c>
-      <c r="O102" s="3" t="n">
+          <t>Valija de Arte Mis Diseños. Monstruos</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="n">
         <v>25850</v>
       </c>
     </row>
@@ -2302,10 +2317,10 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Princesa</t>
-        </is>
-      </c>
-      <c r="O103" s="3" t="n">
+          <t>Valija de Arte Mis Diseños. Nena con Globos</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="n">
         <v>25850</v>
       </c>
     </row>
@@ -2317,10 +2332,10 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Robots</t>
-        </is>
-      </c>
-      <c r="O104" s="3" t="n">
+          <t>Valija de Arte Mis Diseños. Nena en Hamaca</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="n">
         <v>25850</v>
       </c>
     </row>
@@ -2332,48 +2347,48 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Valija de Arte Mis Diseños. Unicornio</t>
-        </is>
-      </c>
-      <c r="O105" s="3" t="n">
+          <t>Valija de Arte Mis Diseños. Princesa</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="n">
         <v>25850</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Valija de Arte Mis Diseños. Robots</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="n">
+        <v>25850</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>VALIJAS DIDÁCTICAS DE ARTE</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Valija de Arte Mis Diseños. Unicornio</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="n">
+        <v>25850</v>
+      </c>
+    </row>
+    <row r="108" ht="28" customHeight="1">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
           <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
         </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Bolsito Chef nena</t>
-        </is>
-      </c>
-      <c r="O107" s="3" t="n">
-        <v>11500</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Bolsito Chef varón</t>
-        </is>
-      </c>
-      <c r="O108" s="3" t="n">
-        <v>11500</v>
       </c>
     </row>
     <row r="109">
@@ -2384,10 +2399,10 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Bolsito Explorador Jirafas</t>
-        </is>
-      </c>
-      <c r="O109" s="3" t="n">
+          <t>Bolsito Chef nena</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="n">
         <v>11500</v>
       </c>
     </row>
@@ -2399,10 +2414,10 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Bolsito Explorador África</t>
-        </is>
-      </c>
-      <c r="O110" s="3" t="n">
+          <t>Bolsito Chef varón</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="n">
         <v>11500</v>
       </c>
     </row>
@@ -2414,10 +2429,10 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Bolsito Mini Peluquería</t>
-        </is>
-      </c>
-      <c r="O111" s="3" t="n">
+          <t>Bolsito Explorador Jirafas</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="n">
         <v>11500</v>
       </c>
     </row>
@@ -2429,11 +2444,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Set de esqueleto y órganos del cuerpo humano para Docentes y Educadores</t>
-        </is>
-      </c>
-      <c r="O112" s="3" t="n">
-        <v>16500</v>
+          <t>Bolsito Explorador África</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="n">
+        <v>11500</v>
       </c>
     </row>
     <row r="113">
@@ -2444,11 +2459,11 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Valija de Mini Chef nena</t>
-        </is>
-      </c>
-      <c r="O113" s="3" t="n">
-        <v>21000</v>
+          <t>Bolsito Mini Peluquería</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="n">
+        <v>11500</v>
       </c>
     </row>
     <row r="114">
@@ -2459,11 +2474,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Valija de Mini Chef varón</t>
-        </is>
-      </c>
-      <c r="O114" s="3" t="n">
-        <v>21000</v>
+          <t>Set de esqueleto y órganos del cuerpo humano para Docentes y Educadores</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="n">
+        <v>16500</v>
       </c>
     </row>
     <row r="115">
@@ -2474,11 +2489,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Valija de Mini Doctor</t>
-        </is>
-      </c>
-      <c r="O115" s="3" t="n">
-        <v>37500</v>
+          <t>Valija de Mini Chef nena</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="n">
+        <v>21000</v>
       </c>
     </row>
     <row r="116">
@@ -2489,11 +2504,11 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Valija de Mini Exploradores</t>
-        </is>
-      </c>
-      <c r="O116" s="3" t="n">
-        <v>24800</v>
+          <t>Valija de Mini Chef varón</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="n">
+        <v>21000</v>
       </c>
     </row>
     <row r="117">
@@ -2504,11 +2519,11 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Valija de Mini Jardineros</t>
-        </is>
-      </c>
-      <c r="O117" s="3" t="n">
-        <v>23500</v>
+          <t>Valija de Mini Doctor</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="n">
+        <v>37500</v>
       </c>
     </row>
     <row r="118">
@@ -2519,11 +2534,11 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Valija de Mini Maestra</t>
-        </is>
-      </c>
-      <c r="O118" s="3" t="n">
-        <v>28600</v>
+          <t>Valija de Mini Exploradores</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="n">
+        <v>24800</v>
       </c>
     </row>
     <row r="119">
@@ -2534,11 +2549,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Valija de Mini Maestro</t>
-        </is>
-      </c>
-      <c r="O119" s="3" t="n">
-        <v>28600</v>
+          <t>Valija de Mini Jardineros</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="120">
@@ -2549,11 +2564,11 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Valija de Mini Spa</t>
-        </is>
-      </c>
-      <c r="O120" s="3" t="n">
-        <v>29800</v>
+          <t>Valija de Mini Maestra</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="n">
+        <v>28600</v>
       </c>
     </row>
     <row r="121">
@@ -2564,11 +2579,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Valija de Mini Veterinarios</t>
-        </is>
-      </c>
-      <c r="O121" s="3" t="n">
-        <v>26400</v>
+          <t>Valija de Mini Maestro</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="n">
+        <v>28600</v>
       </c>
     </row>
     <row r="122">
@@ -2579,11 +2594,11 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Valija de Tarde de Mate</t>
-        </is>
-      </c>
-      <c r="O122" s="3" t="n">
-        <v>19500</v>
+          <t>Valija de Mini Spa</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="n">
+        <v>29800</v>
       </c>
     </row>
     <row r="123">
@@ -2594,48 +2609,48 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Valija de Tardes de Té</t>
-        </is>
-      </c>
-      <c r="O123" s="3" t="n">
-        <v>25000</v>
+          <t>Valija de Mini Veterinarios</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="n">
+        <v>26400</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Valija de Tarde de Mate</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="n">
+        <v>19500</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
+          <t>VALIJAS DIDÁCTICAS DE OFICIO</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Valija de Tardes de Té</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="126" ht="28" customHeight="1">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
           <t>DISFRACES PARA NENAS</t>
         </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Disfraz de Anna (Frozen)</t>
-        </is>
-      </c>
-      <c r="O125" s="3" t="n">
-        <v>24850</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>DISFRACES PARA NENAS</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Disfraz de Bella</t>
-        </is>
-      </c>
-      <c r="O126" s="3" t="n">
-        <v>23970</v>
       </c>
     </row>
     <row r="127">
@@ -2646,10 +2661,10 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Disfraz de Blancanieves</t>
-        </is>
-      </c>
-      <c r="O127" s="3" t="n">
+          <t>Disfraz de Anna (Frozen)</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="n">
         <v>24850</v>
       </c>
     </row>
@@ -2661,10 +2676,10 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Disfraz de Cenicienta</t>
-        </is>
-      </c>
-      <c r="O128" s="3" t="n">
+          <t>Disfraz de Bella</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="n">
         <v>23970</v>
       </c>
     </row>
@@ -2676,10 +2691,10 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Disfraz de Elsa (Frozen)</t>
-        </is>
-      </c>
-      <c r="O129" s="3" t="n">
+          <t>Disfraz de Blancanieves</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="n">
         <v>24850</v>
       </c>
     </row>
@@ -2691,11 +2706,11 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Disfraz de Mira K-Pop Demon Hunters</t>
-        </is>
-      </c>
-      <c r="O130" s="3" t="n">
-        <v>38500</v>
+          <t>Disfraz de Cenicienta</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="n">
+        <v>23970</v>
       </c>
     </row>
     <row r="131">
@@ -2706,11 +2721,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Disfraz de Moana</t>
-        </is>
-      </c>
-      <c r="O131" s="3" t="n">
-        <v>24500</v>
+          <t>Disfraz de Elsa (Frozen)</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="n">
+        <v>24850</v>
       </c>
     </row>
     <row r="132">
@@ -2721,11 +2736,11 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Disfraz de Mujer Maravilla</t>
-        </is>
-      </c>
-      <c r="O132" s="3" t="n">
-        <v>19850</v>
+          <t>Disfraz de Mira K-Pop Demon Hunters</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="n">
+        <v>38500</v>
       </c>
     </row>
     <row r="133">
@@ -2736,11 +2751,11 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Disfraz de Princesa Aurora,  La Bella Durmiente</t>
-        </is>
-      </c>
-      <c r="O133" s="3" t="n">
-        <v>23970</v>
+          <t>Disfraz de Moana</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="n">
+        <v>24500</v>
       </c>
     </row>
     <row r="134">
@@ -2751,11 +2766,11 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Disfraz de Rapunzel Encantada</t>
-        </is>
-      </c>
-      <c r="O134" s="3" t="n">
-        <v>33300</v>
+          <t>Disfraz de Mujer Maravilla</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="n">
+        <v>19850</v>
       </c>
     </row>
     <row r="135">
@@ -2766,11 +2781,11 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Disfraz de Rumi K-Pop Demon Hunters</t>
-        </is>
-      </c>
-      <c r="O135" s="3" t="n">
-        <v>28500</v>
+          <t>Disfraz de Princesa Aurora,  La Bella Durmiente</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="n">
+        <v>23970</v>
       </c>
     </row>
     <row r="136">
@@ -2781,11 +2796,11 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Disfraz de Rumi K-Pop Demon Hunters (Traje de colores con Chaqueta amarilla)</t>
-        </is>
-      </c>
-      <c r="O136" s="3" t="n">
-        <v>51800</v>
+          <t>Disfraz de Rapunzel Encantada</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="n">
+        <v>33300</v>
       </c>
     </row>
     <row r="137">
@@ -2796,11 +2811,11 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Disfraz de Rumi K-Pop Demon Hunters, con Chaqueta y encanto dorado</t>
-        </is>
-      </c>
-      <c r="O137" s="3" t="n">
-        <v>53200</v>
+          <t>Disfraz de Rumi K-Pop Demon Hunters</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="n">
+        <v>28500</v>
       </c>
     </row>
     <row r="138">
@@ -2811,11 +2826,11 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Disfraz de Sirenita</t>
-        </is>
-      </c>
-      <c r="O138" s="3" t="n">
-        <v>22500</v>
+          <t>Disfraz de Rumi K-Pop Demon Hunters (Traje de colores con Chaqueta amarilla)</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="n">
+        <v>51800</v>
       </c>
     </row>
     <row r="139">
@@ -2826,11 +2841,11 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Disfraz de Unicornio Mágico</t>
-        </is>
-      </c>
-      <c r="O139" s="3" t="n">
-        <v>27400</v>
+          <t>Disfraz de Rumi K-Pop Demon Hunters, con Chaqueta y encanto dorado</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="n">
+        <v>53200</v>
       </c>
     </row>
     <row r="140">
@@ -2841,11 +2856,11 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Disfraz de Zoey  K-Pop Demon Hunters</t>
-        </is>
-      </c>
-      <c r="O140" s="3" t="n">
-        <v>45000</v>
+          <t>Disfraz de Sirenita</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="n">
+        <v>22500</v>
       </c>
     </row>
     <row r="141">
@@ -2856,11 +2871,11 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Tutú de Bailarina Unicornio</t>
-        </is>
-      </c>
-      <c r="O141" s="3" t="n">
-        <v>23200</v>
+          <t>Disfraz de Unicornio Mágico</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="n">
+        <v>27400</v>
       </c>
     </row>
     <row r="142">
@@ -2871,48 +2886,48 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Tutú de bailarina</t>
-        </is>
-      </c>
-      <c r="O142" s="3" t="n">
-        <v>19500</v>
+          <t>Disfraz de Zoey  K-Pop Demon Hunters</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="n">
+        <v>45000</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>DISFRACES PARA NENES</t>
-        </is>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Tutú de Bailarina Unicornio</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="n">
+        <v>23200</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
+          <t>DISFRACES PARA NENAS</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Tutú de bailarina</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="n">
+        <v>19500</v>
+      </c>
+    </row>
+    <row r="145" ht="28" customHeight="1">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
           <t>DISFRACES PARA NENES</t>
         </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Disfraz de Batman</t>
-        </is>
-      </c>
-      <c r="O144" s="3" t="n">
-        <v>23500</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>DISFRACES PARA NENES</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Disfraz de Bombero</t>
-        </is>
-      </c>
-      <c r="O145" s="3" t="n">
-        <v>15000</v>
       </c>
     </row>
     <row r="146">
@@ -2923,10 +2938,10 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Disfraz de Capitán América</t>
-        </is>
-      </c>
-      <c r="O146" s="3" t="n">
+          <t>Disfraz de Batman</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="n">
         <v>23500</v>
       </c>
     </row>
@@ -2938,11 +2953,11 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Disfraz de Hombre Araña</t>
-        </is>
-      </c>
-      <c r="O147" s="3" t="n">
-        <v>18000</v>
+          <t>Disfraz de Bombero</t>
+        </is>
+      </c>
+      <c r="C147" s="7" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="148">
@@ -2953,11 +2968,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Disfraz de Pirata</t>
-        </is>
-      </c>
-      <c r="O148" s="3" t="n">
-        <v>18000</v>
+          <t>Disfraz de Capitán América</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="149">
@@ -2968,11 +2983,11 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Disfraz de Policía</t>
-        </is>
-      </c>
-      <c r="O149" s="3" t="n">
-        <v>15000</v>
+          <t>Disfraz de Hombre Araña</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="150">
@@ -2983,48 +2998,48 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Disfraz de Superman</t>
-        </is>
-      </c>
-      <c r="O150" s="3" t="n">
-        <v>22000</v>
+          <t>Disfraz de Pirata</t>
+        </is>
+      </c>
+      <c r="C150" s="7" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>DISFRACES DE ANIMALITOS</t>
-        </is>
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>DISFRACES PARA NENES</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Disfraz de Policía</t>
+        </is>
+      </c>
+      <c r="C151" s="7" t="n">
+        <v>15000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
+          <t>DISFRACES PARA NENES</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Disfraz de Superman</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="n">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="153" ht="28" customHeight="1">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
           <t>DISFRACES DE ANIMALITOS</t>
         </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Disfraz de Araña</t>
-        </is>
-      </c>
-      <c r="O152" s="3" t="n">
-        <v>23500</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>DISFRACES DE ANIMALITOS</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Disfraz de Cebra</t>
-        </is>
-      </c>
-      <c r="O153" s="3" t="n">
-        <v>23500</v>
       </c>
     </row>
     <row r="154">
@@ -3035,11 +3050,11 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Disfraz de Dinosaurio</t>
-        </is>
-      </c>
-      <c r="O154" s="3" t="n">
-        <v>25200</v>
+          <t>Disfraz de Araña</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="155">
@@ -3050,48 +3065,48 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Disfraz de Tigre</t>
-        </is>
-      </c>
-      <c r="O155" s="3" t="n">
+          <t>Disfraz de Cebra</t>
+        </is>
+      </c>
+      <c r="C155" s="7" t="n">
         <v>23500</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>DISFRACES DE ANIMALITOS</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Disfraz de Dinosaurio</t>
+        </is>
+      </c>
+      <c r="C156" s="7" t="n">
+        <v>25200</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
+          <t>DISFRACES DE ANIMALITOS</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Disfraz de Tigre</t>
+        </is>
+      </c>
+      <c r="C157" s="7" t="n">
+        <v>23500</v>
+      </c>
+    </row>
+    <row r="158" ht="28" customHeight="1">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
           <t>DISFRACES DE HALLOWEEN</t>
         </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Caramelera Calabaza</t>
-        </is>
-      </c>
-      <c r="O157" s="3" t="n">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>DISFRACES DE HALLOWEEN</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Disfraz de Araña</t>
-        </is>
-      </c>
-      <c r="O158" s="3" t="n">
-        <v>23500</v>
       </c>
     </row>
     <row r="159">
@@ -3102,11 +3117,11 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Fuxia</t>
-        </is>
-      </c>
-      <c r="O159" s="3" t="n">
-        <v>25500</v>
+          <t>Caramelera Calabaza</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="160">
@@ -3117,11 +3132,11 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Naranja</t>
-        </is>
-      </c>
-      <c r="O160" s="3" t="n">
-        <v>25500</v>
+          <t>Disfraz de Araña</t>
+        </is>
+      </c>
+      <c r="C160" s="7" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="161">
@@ -3132,10 +3147,10 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Verde</t>
-        </is>
-      </c>
-      <c r="O161" s="3" t="n">
+          <t>Disfraz de Brujita Fuxia</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="n">
         <v>25500</v>
       </c>
     </row>
@@ -3147,10 +3162,10 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Disfraz de Brujita Violeta</t>
-        </is>
-      </c>
-      <c r="O162" s="3" t="n">
+          <t>Disfraz de Brujita Naranja</t>
+        </is>
+      </c>
+      <c r="C162" s="7" t="n">
         <v>25500</v>
       </c>
     </row>
@@ -3162,11 +3177,11 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Disfraz de Calabaza</t>
-        </is>
-      </c>
-      <c r="O163" s="3" t="n">
-        <v>23500</v>
+          <t>Disfraz de Brujita Verde</t>
+        </is>
+      </c>
+      <c r="C163" s="7" t="n">
+        <v>25500</v>
       </c>
     </row>
     <row r="164">
@@ -3177,11 +3192,11 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Disfraz de Esqueleto</t>
-        </is>
-      </c>
-      <c r="O164" s="3" t="n">
-        <v>25000</v>
+          <t>Disfraz de Brujita Violeta</t>
+        </is>
+      </c>
+      <c r="C164" s="7" t="n">
+        <v>25500</v>
       </c>
     </row>
     <row r="165">
@@ -3192,11 +3207,11 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Disfraz de Merlina</t>
-        </is>
-      </c>
-      <c r="O165" s="3" t="n">
-        <v>32000</v>
+          <t>Disfraz de Calabaza</t>
+        </is>
+      </c>
+      <c r="C165" s="7" t="n">
+        <v>23500</v>
       </c>
     </row>
     <row r="166">
@@ -3207,48 +3222,48 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Disfraz de Vampira</t>
-        </is>
-      </c>
-      <c r="O166" s="3" t="n">
-        <v>25300</v>
+          <t>Disfraz de Esqueleto</t>
+        </is>
+      </c>
+      <c r="C166" s="7" t="n">
+        <v>25000</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Disfraz de Merlina</t>
+        </is>
+      </c>
+      <c r="C167" s="7" t="n">
+        <v>32000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
+          <t>DISFRACES DE HALLOWEEN</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Disfraz de Vampira</t>
+        </is>
+      </c>
+      <c r="C168" s="7" t="n">
+        <v>25300</v>
+      </c>
+    </row>
+    <row r="169" ht="28" customHeight="1">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
           <t>JUGUETES PARA BEBÉS</t>
         </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Cesto para juguetes Cactus</t>
-        </is>
-      </c>
-      <c r="O168" s="3" t="n">
-        <v>22900</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>JUGUETES PARA BEBÉS</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Cesto para juguetes Cebra y Jirafa</t>
-        </is>
-      </c>
-      <c r="O169" s="3" t="n">
-        <v>22900</v>
       </c>
     </row>
     <row r="170">
@@ -3259,10 +3274,10 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Cesto para juguetes Gatitos</t>
-        </is>
-      </c>
-      <c r="O170" s="3" t="n">
+          <t>Cesto para juguetes Cactus</t>
+        </is>
+      </c>
+      <c r="C170" s="7" t="n">
         <v>22900</v>
       </c>
     </row>
@@ -3274,10 +3289,10 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Cesto para juguetes Indi</t>
-        </is>
-      </c>
-      <c r="O171" s="3" t="n">
+          <t>Cesto para juguetes Cebra y Jirafa</t>
+        </is>
+      </c>
+      <c r="C171" s="7" t="n">
         <v>22900</v>
       </c>
     </row>
@@ -3289,11 +3304,11 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Globo Pelota Animalitos</t>
-        </is>
-      </c>
-      <c r="O172" s="3" t="n">
-        <v>6800</v>
+          <t>Cesto para juguetes Gatitos</t>
+        </is>
+      </c>
+      <c r="C172" s="7" t="n">
+        <v>22900</v>
       </c>
     </row>
     <row r="173">
@@ -3304,11 +3319,11 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Globo Pelota Dinosaurios</t>
-        </is>
-      </c>
-      <c r="O173" s="3" t="n">
-        <v>6800</v>
+          <t>Cesto para juguetes Indi</t>
+        </is>
+      </c>
+      <c r="C173" s="7" t="n">
+        <v>22900</v>
       </c>
     </row>
     <row r="174">
@@ -3319,10 +3334,10 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Globo Pelota Gatitos</t>
-        </is>
-      </c>
-      <c r="O174" s="3" t="n">
+          <t>Globo Pelota Animalitos</t>
+        </is>
+      </c>
+      <c r="C174" s="7" t="n">
         <v>6800</v>
       </c>
     </row>
@@ -3334,10 +3349,10 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Globo Pelota Haditas</t>
-        </is>
-      </c>
-      <c r="O175" s="3" t="n">
+          <t>Globo Pelota Dinosaurios</t>
+        </is>
+      </c>
+      <c r="C175" s="7" t="n">
         <v>6800</v>
       </c>
     </row>
@@ -3349,10 +3364,10 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Globo Pelota Monstruos</t>
-        </is>
-      </c>
-      <c r="O176" s="3" t="n">
+          <t>Globo Pelota Gatitos</t>
+        </is>
+      </c>
+      <c r="C176" s="7" t="n">
         <v>6800</v>
       </c>
     </row>
@@ -3364,10 +3379,10 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Globo Pelota Selva</t>
-        </is>
-      </c>
-      <c r="O177" s="3" t="n">
+          <t>Globo Pelota Haditas</t>
+        </is>
+      </c>
+      <c r="C177" s="7" t="n">
         <v>6800</v>
       </c>
     </row>
@@ -3379,11 +3394,11 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Libro para bebé "Coral"</t>
-        </is>
-      </c>
-      <c r="O178" s="3" t="n">
-        <v>8400</v>
+          <t>Globo Pelota Monstruos</t>
+        </is>
+      </c>
+      <c r="C178" s="7" t="n">
+        <v>6800</v>
       </c>
     </row>
     <row r="179">
@@ -3394,11 +3409,11 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Libro para bebé "Cosquillitas"</t>
-        </is>
-      </c>
-      <c r="O179" s="3" t="n">
-        <v>8400</v>
+          <t>Globo Pelota Selva</t>
+        </is>
+      </c>
+      <c r="C179" s="7" t="n">
+        <v>6800</v>
       </c>
     </row>
     <row r="180">
@@ -3409,10 +3424,10 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Libro para bebé "Mariposas"</t>
-        </is>
-      </c>
-      <c r="O180" s="3" t="n">
+          <t>Libro para bebé "Coral"</t>
+        </is>
+      </c>
+      <c r="C180" s="7" t="n">
         <v>8400</v>
       </c>
     </row>
@@ -3424,11 +3439,11 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Manta para bebé "Animalitos de la Selva"</t>
-        </is>
-      </c>
-      <c r="O181" s="3" t="n">
-        <v>15600</v>
+          <t>Libro para bebé "Cosquillitas"</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="n">
+        <v>8400</v>
       </c>
     </row>
     <row r="182">
@@ -3439,11 +3454,11 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Manta para bebé "La Ciudad"</t>
-        </is>
-      </c>
-      <c r="O182" s="3" t="n">
-        <v>15600</v>
+          <t>Libro para bebé "Mariposas"</t>
+        </is>
+      </c>
+      <c r="C182" s="7" t="n">
+        <v>8400</v>
       </c>
     </row>
     <row r="183">
@@ -3454,10 +3469,10 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Manta para bebé "Mininos"</t>
-        </is>
-      </c>
-      <c r="O183" s="3" t="n">
+          <t>Manta para bebé "Animalitos de la Selva"</t>
+        </is>
+      </c>
+      <c r="C183" s="7" t="n">
         <v>15600</v>
       </c>
     </row>
@@ -3469,11 +3484,11 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Pelota de Trapo  Animalitos</t>
-        </is>
-      </c>
-      <c r="O184" s="3" t="n">
-        <v>15950</v>
+          <t>Manta para bebé "La Ciudad"</t>
+        </is>
+      </c>
+      <c r="C184" s="7" t="n">
+        <v>15600</v>
       </c>
     </row>
     <row r="185">
@@ -3484,11 +3499,11 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Pelota de Trapo  Dinosaurios</t>
-        </is>
-      </c>
-      <c r="O185" s="3" t="n">
-        <v>15950</v>
+          <t>Manta para bebé "Mininos"</t>
+        </is>
+      </c>
+      <c r="C185" s="7" t="n">
+        <v>15600</v>
       </c>
     </row>
     <row r="186">
@@ -3499,10 +3514,10 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Pelota de Trapo Gatitos</t>
-        </is>
-      </c>
-      <c r="O186" s="3" t="n">
+          <t>Pelota de Trapo  Animalitos</t>
+        </is>
+      </c>
+      <c r="C186" s="7" t="n">
         <v>15950</v>
       </c>
     </row>
@@ -3514,10 +3529,10 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Pelota de Trapo Selva</t>
-        </is>
-      </c>
-      <c r="O187" s="3" t="n">
+          <t>Pelota de Trapo  Dinosaurios</t>
+        </is>
+      </c>
+      <c r="C187" s="7" t="n">
         <v>15950</v>
       </c>
     </row>
@@ -3529,11 +3544,11 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Pulpitos Reversibles con dos emociones (alegre/ enojado)</t>
-        </is>
-      </c>
-      <c r="O188" s="3" t="n">
-        <v>7500</v>
+          <t>Pelota de Trapo Gatitos</t>
+        </is>
+      </c>
+      <c r="C188" s="7" t="n">
+        <v>15950</v>
       </c>
     </row>
     <row r="189">
@@ -3544,48 +3559,48 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Rayuela de tela para aprender los números jugando</t>
-        </is>
-      </c>
-      <c r="O189" s="3" t="n">
-        <v>24500</v>
+          <t>Pelota de Trapo Selva</t>
+        </is>
+      </c>
+      <c r="C189" s="7" t="n">
+        <v>15950</v>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Pulpitos Reversibles con dos emociones (alegre/ enojado)</t>
+        </is>
+      </c>
+      <c r="C190" s="7" t="n">
+        <v>7500</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
+          <t>JUGUETES PARA BEBÉS</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Rayuela de tela para aprender los números jugando</t>
+        </is>
+      </c>
+      <c r="C191" s="7" t="n">
+        <v>24500</v>
+      </c>
+    </row>
+    <row r="192" ht="28" customHeight="1">
+      <c r="A192" s="6" t="inlineStr">
+        <is>
           <t>MUÑECAS DE TRAPO</t>
         </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Muñeca Piccolina Aurora</t>
-        </is>
-      </c>
-      <c r="O191" s="3" t="n">
-        <v>24350</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>MUÑECAS DE TRAPO</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Muñeca Piccolina Bella</t>
-        </is>
-      </c>
-      <c r="O192" s="3" t="n">
-        <v>24350</v>
       </c>
     </row>
     <row r="193">
@@ -3596,10 +3611,10 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Blancanieves</t>
-        </is>
-      </c>
-      <c r="O193" s="3" t="n">
+          <t>Muñeca Piccolina Aurora</t>
+        </is>
+      </c>
+      <c r="C193" s="7" t="n">
         <v>24350</v>
       </c>
     </row>
@@ -3611,10 +3626,10 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Cenicienta</t>
-        </is>
-      </c>
-      <c r="O194" s="3" t="n">
+          <t>Muñeca Piccolina Bella</t>
+        </is>
+      </c>
+      <c r="C194" s="7" t="n">
         <v>24350</v>
       </c>
     </row>
@@ -3626,10 +3641,10 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Coqueta</t>
-        </is>
-      </c>
-      <c r="O195" s="3" t="n">
+          <t>Muñeca Piccolina Blancanieves</t>
+        </is>
+      </c>
+      <c r="C195" s="7" t="n">
         <v>24350</v>
       </c>
     </row>
@@ -3641,10 +3656,10 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Deportiva</t>
-        </is>
-      </c>
-      <c r="O196" s="3" t="n">
+          <t>Muñeca Piccolina Cenicienta</t>
+        </is>
+      </c>
+      <c r="C196" s="7" t="n">
         <v>24350</v>
       </c>
     </row>
@@ -3656,10 +3671,10 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Folk</t>
-        </is>
-      </c>
-      <c r="O197" s="3" t="n">
+          <t>Muñeca Piccolina Coqueta</t>
+        </is>
+      </c>
+      <c r="C197" s="7" t="n">
         <v>24350</v>
       </c>
     </row>
@@ -3671,10 +3686,10 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Jardinera</t>
-        </is>
-      </c>
-      <c r="O198" s="3" t="n">
+          <t>Muñeca Piccolina Deportiva</t>
+        </is>
+      </c>
+      <c r="C198" s="7" t="n">
         <v>24350</v>
       </c>
     </row>
@@ -3686,10 +3701,10 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Rapunsel</t>
-        </is>
-      </c>
-      <c r="O199" s="3" t="n">
+          <t>Muñeca Piccolina Folk</t>
+        </is>
+      </c>
+      <c r="C199" s="7" t="n">
         <v>24350</v>
       </c>
     </row>
@@ -3701,10 +3716,10 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Romántica</t>
-        </is>
-      </c>
-      <c r="O200" s="3" t="n">
+          <t>Muñeca Piccolina Jardinera</t>
+        </is>
+      </c>
+      <c r="C200" s="7" t="n">
         <v>24350</v>
       </c>
     </row>
@@ -3716,10 +3731,10 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina Sofía</t>
-        </is>
-      </c>
-      <c r="O201" s="3" t="n">
+          <t>Muñeca Piccolina Rapunsel</t>
+        </is>
+      </c>
+      <c r="C201" s="7" t="n">
         <v>24350</v>
       </c>
     </row>
@@ -3731,10 +3746,10 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Muñeca Piccolina doctora</t>
-        </is>
-      </c>
-      <c r="O202" s="3" t="n">
+          <t>Muñeca Piccolina Romántica</t>
+        </is>
+      </c>
+      <c r="C202" s="7" t="n">
         <v>24350</v>
       </c>
     </row>
@@ -3746,11 +3761,11 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Traje de doctora para muñecas</t>
-        </is>
-      </c>
-      <c r="O203" s="3" t="n">
-        <v>8300</v>
+          <t>Muñeca Piccolina Sofía</t>
+        </is>
+      </c>
+      <c r="C203" s="7" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="204">
@@ -3761,11 +3776,11 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Traje de jardinera para muñecas</t>
-        </is>
-      </c>
-      <c r="O204" s="3" t="n">
-        <v>8300</v>
+          <t>Muñeca Piccolina doctora</t>
+        </is>
+      </c>
+      <c r="C204" s="7" t="n">
+        <v>24350</v>
       </c>
     </row>
     <row r="205">
@@ -3776,10 +3791,10 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Traje deportivo para muñecas</t>
-        </is>
-      </c>
-      <c r="O205" s="3" t="n">
+          <t>Traje de doctora para muñecas</t>
+        </is>
+      </c>
+      <c r="C205" s="7" t="n">
         <v>8300</v>
       </c>
     </row>
@@ -3791,10 +3806,10 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Vestido campesino para muñecas</t>
-        </is>
-      </c>
-      <c r="O206" s="3" t="n">
+          <t>Traje de jardinera para muñecas</t>
+        </is>
+      </c>
+      <c r="C206" s="7" t="n">
         <v>8300</v>
       </c>
     </row>
@@ -3806,10 +3821,10 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Vestido coqueta para muñecas</t>
-        </is>
-      </c>
-      <c r="O207" s="3" t="n">
+          <t>Traje deportivo para muñecas</t>
+        </is>
+      </c>
+      <c r="C207" s="7" t="n">
         <v>8300</v>
       </c>
     </row>
@@ -3821,10 +3836,10 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Vestido de Aurora para muñecas</t>
-        </is>
-      </c>
-      <c r="O208" s="3" t="n">
+          <t>Vestido campesino para muñecas</t>
+        </is>
+      </c>
+      <c r="C208" s="7" t="n">
         <v>8300</v>
       </c>
     </row>
@@ -3836,10 +3851,10 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Vestido de Bella para muñecas</t>
-        </is>
-      </c>
-      <c r="O209" s="3" t="n">
+          <t>Vestido coqueta para muñecas</t>
+        </is>
+      </c>
+      <c r="C209" s="7" t="n">
         <v>8300</v>
       </c>
     </row>
@@ -3851,10 +3866,10 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Vestido de Blancanieves para muñecas</t>
-        </is>
-      </c>
-      <c r="O210" s="3" t="n">
+          <t>Vestido de Aurora para muñecas</t>
+        </is>
+      </c>
+      <c r="C210" s="7" t="n">
         <v>8300</v>
       </c>
     </row>
@@ -3866,10 +3881,10 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Vestido de Cenicienta para muñecas</t>
-        </is>
-      </c>
-      <c r="O211" s="3" t="n">
+          <t>Vestido de Bella para muñecas</t>
+        </is>
+      </c>
+      <c r="C211" s="7" t="n">
         <v>8300</v>
       </c>
     </row>
@@ -3881,10 +3896,10 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Vestido de Princesa Sofía para muñecas</t>
-        </is>
-      </c>
-      <c r="O212" s="3" t="n">
+          <t>Vestido de Blancanieves para muñecas</t>
+        </is>
+      </c>
+      <c r="C212" s="7" t="n">
         <v>8300</v>
       </c>
     </row>
@@ -3896,10 +3911,10 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Vestido de Rapunzel para muñecas</t>
-        </is>
-      </c>
-      <c r="O213" s="3" t="n">
+          <t>Vestido de Cenicienta para muñecas</t>
+        </is>
+      </c>
+      <c r="C213" s="7" t="n">
         <v>8300</v>
       </c>
     </row>
@@ -3911,26 +3926,59 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
+          <t>Vestido de Princesa Sofía para muñecas</t>
+        </is>
+      </c>
+      <c r="C214" s="7" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Vestido de Rapunzel para muñecas</t>
+        </is>
+      </c>
+      <c r="C215" s="7" t="n">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>MUÑECAS DE TRAPO</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
           <t>Vestido romántico para muñecas</t>
         </is>
       </c>
-      <c r="O214" s="3" t="n">
+      <c r="C216" s="7" t="n">
         <v>8300</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A156:O156"/>
-    <mergeCell ref="A190:O190"/>
-    <mergeCell ref="A86:O86"/>
-    <mergeCell ref="A28:O28"/>
-    <mergeCell ref="A151:O151"/>
-    <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A167:O167"/>
-    <mergeCell ref="A50:O50"/>
-    <mergeCell ref="A143:O143"/>
-    <mergeCell ref="A106:O106"/>
-    <mergeCell ref="A124:O124"/>
+  <mergeCells count="14">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A108:M108"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A169:M169"/>
+    <mergeCell ref="A126:M126"/>
+    <mergeCell ref="A158:M158"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A88:M88"/>
+    <mergeCell ref="A145:M145"/>
+    <mergeCell ref="A153:M153"/>
+    <mergeCell ref="A30:M30"/>
+    <mergeCell ref="A192:M192"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A52:M52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
